--- a/docs/设计文档.xlsx
+++ b/docs/设计文档.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="367">
   <si>
     <t>名称</t>
   </si>
@@ -913,6 +913,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>注意能力需要可以叠加</t>
     </r>
     <r>
@@ -992,6 +998,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>关键字</t>
     </r>
     <r>
@@ -1077,6 +1089,16 @@
     <t>基础伤害+2，愈合层数+1</t>
   </si>
   <si>
+    <t>跨过黑夜的晨曦</t>
+  </si>
+  <si>
+    <t>造成30点伤害
+叠加3：耗能减少2</t>
+  </si>
+  <si>
+    <t>基础伤害+10</t>
+  </si>
+  <si>
     <t>说明</t>
   </si>
   <si>
@@ -1240,6 +1262,9 @@
   <si>
     <t>能量使用能量图标显示
 剩余层数表示下次获得能量还需要打出的共鸣攻击牌数量，触发后重置层数</t>
+  </si>
+  <si>
+    <t>触发叠加效果时，抽X张牌</t>
   </si>
   <si>
     <t>类型/稀有度</t>
@@ -2013,7 +2038,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2024,14 +2049,14 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2081,9 +2106,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2502,21 +2524,21 @@
       <c r="D2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>14</v>
       </c>
       <c r="F2" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H2" s="16"/>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4" t="s">
+      <c r="J2" s="3"/>
+      <c r="K2" s="3" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2533,21 +2555,21 @@
       <c r="D3" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F3" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H3" s="16"/>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4" t="s">
+      <c r="J3" s="3"/>
+      <c r="K3" s="3" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2564,21 +2586,21 @@
       <c r="D4" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F4" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H4" s="16"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="4" t="s">
+      <c r="I4" s="2"/>
+      <c r="J4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="4"/>
+      <c r="K4" s="3"/>
     </row>
     <row r="5" ht="28" spans="1:11">
       <c r="A5" s="14" t="s">
@@ -2593,21 +2615,21 @@
       <c r="D5" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F5" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H5" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
     </row>
     <row r="6" ht="28" spans="1:11">
       <c r="A6" s="17" t="s">
@@ -2622,23 +2644,23 @@
       <c r="D6" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F6" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H6" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="I6" s="3"/>
-      <c r="J6" s="4" t="s">
+      <c r="I6" s="2"/>
+      <c r="J6" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="3" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2655,21 +2677,21 @@
       <c r="D7" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F7" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H7" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="I7" s="3"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
     </row>
     <row r="8" ht="28" spans="1:11">
       <c r="A8" s="17" t="s">
@@ -2684,23 +2706,23 @@
       <c r="D8" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F8" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H8" s="16"/>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="K8" s="4"/>
+      <c r="K8" s="3"/>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="17" t="s">
@@ -2715,21 +2737,21 @@
       <c r="D9" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>45</v>
       </c>
       <c r="F9" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H9" s="16"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="4" t="s">
+      <c r="I9" s="2"/>
+      <c r="J9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="K9" s="4"/>
+      <c r="K9" s="3"/>
     </row>
     <row r="10" ht="42" spans="1:11">
       <c r="A10" s="17" t="s">
@@ -2744,21 +2766,21 @@
       <c r="D10" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F10" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H10" s="16"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="4" t="s">
+      <c r="I10" s="2"/>
+      <c r="J10" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="K10" s="4"/>
+      <c r="K10" s="3"/>
     </row>
     <row r="11" ht="42" spans="1:11">
       <c r="A11" s="17" t="s">
@@ -2773,23 +2795,23 @@
       <c r="D11" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>52</v>
       </c>
       <c r="F11" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H11" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="I11" s="3"/>
-      <c r="J11" s="4" t="s">
+      <c r="I11" s="2"/>
+      <c r="J11" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="K11" s="4"/>
+      <c r="K11" s="3"/>
     </row>
     <row r="12" ht="28" spans="1:11">
       <c r="A12" s="17" t="s">
@@ -2804,21 +2826,21 @@
       <c r="D12" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>56</v>
       </c>
       <c r="F12" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H12" s="16"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="4" t="s">
+      <c r="I12" s="2"/>
+      <c r="J12" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="K12" s="4"/>
+      <c r="K12" s="3"/>
     </row>
     <row r="13" ht="42" spans="1:11">
       <c r="A13" s="17" t="s">
@@ -2833,23 +2855,23 @@
       <c r="D13" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>59</v>
       </c>
       <c r="F13" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="2" t="s">
         <v>61</v>
       </c>
       <c r="H13" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="I13" s="3"/>
-      <c r="J13" s="4" t="s">
+      <c r="I13" s="2"/>
+      <c r="J13" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="K13" s="4"/>
+      <c r="K13" s="3"/>
     </row>
     <row r="14" ht="42" spans="1:11">
       <c r="A14" s="17" t="s">
@@ -2864,21 +2886,21 @@
       <c r="D14" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F14" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H14" s="16"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="4" t="s">
+      <c r="I14" s="2"/>
+      <c r="J14" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="K14" s="4"/>
+      <c r="K14" s="3"/>
     </row>
     <row r="15" ht="28" spans="1:11">
       <c r="A15" s="17" t="s">
@@ -2893,21 +2915,21 @@
       <c r="D15" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="3" t="s">
         <v>66</v>
       </c>
       <c r="F15" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H15" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="I15" s="3"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
     </row>
     <row r="16" ht="42" spans="1:11">
       <c r="A16" s="17" t="s">
@@ -2922,23 +2944,23 @@
       <c r="D16" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="3" t="s">
         <v>70</v>
       </c>
       <c r="F16" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="2" t="s">
         <v>61</v>
       </c>
       <c r="H16" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="I16" s="3"/>
-      <c r="J16" s="4" t="s">
+      <c r="I16" s="2"/>
+      <c r="J16" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="K16" s="4"/>
+      <c r="K16" s="3"/>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="17" t="s">
@@ -2953,21 +2975,21 @@
       <c r="D17" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="3" t="s">
         <v>73</v>
       </c>
       <c r="F17" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="G17" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H17" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="I17" s="3"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
     </row>
     <row r="18" ht="28" spans="1:11">
       <c r="A18" s="17" t="s">
@@ -2982,23 +3004,23 @@
       <c r="D18" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="3" t="s">
         <v>76</v>
       </c>
       <c r="F18" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G18" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H18" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="I18" s="3"/>
-      <c r="J18" s="4" t="s">
+      <c r="I18" s="2"/>
+      <c r="J18" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="K18" s="4" t="s">
+      <c r="K18" s="3" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3015,23 +3037,23 @@
       <c r="D19" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="3" t="s">
         <v>80</v>
       </c>
       <c r="F19" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="G19" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H19" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="I19" s="3"/>
-      <c r="J19" s="4" t="s">
+      <c r="I19" s="2"/>
+      <c r="J19" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K19" s="4"/>
+      <c r="K19" s="3"/>
     </row>
     <row r="20" ht="28" spans="1:11">
       <c r="A20" s="19" t="s">
@@ -3046,21 +3068,21 @@
       <c r="D20" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="3" t="s">
         <v>85</v>
       </c>
       <c r="F20" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="G20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H20" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="I20" s="3"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="4" t="s">
+      <c r="I20" s="2"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3" t="s">
         <v>88</v>
       </c>
     </row>
@@ -3077,21 +3099,21 @@
       <c r="D21" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="3" t="s">
         <v>90</v>
       </c>
       <c r="F21" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="G21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H21" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="I21" s="3"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="4"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
     </row>
     <row r="22" ht="42" spans="1:11">
       <c r="A22" s="19" t="s">
@@ -3106,23 +3128,23 @@
       <c r="D22" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="3" t="s">
         <v>93</v>
       </c>
       <c r="F22" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="G22" s="2" t="s">
         <v>61</v>
       </c>
       <c r="H22" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="I22" s="3"/>
-      <c r="J22" s="4" t="s">
+      <c r="I22" s="2"/>
+      <c r="J22" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="K22" s="4"/>
+      <c r="K22" s="3"/>
     </row>
     <row r="23" ht="28" spans="1:11">
       <c r="A23" s="19" t="s">
@@ -3137,23 +3159,23 @@
       <c r="D23" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="3" t="s">
         <v>97</v>
       </c>
       <c r="F23" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="G23" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H23" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="I23" s="3"/>
-      <c r="J23" s="4" t="s">
+      <c r="I23" s="2"/>
+      <c r="J23" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K23" s="4"/>
+      <c r="K23" s="3"/>
     </row>
     <row r="24" ht="28" spans="1:11">
       <c r="A24" s="19" t="s">
@@ -3168,23 +3190,23 @@
       <c r="D24" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="3" t="s">
         <v>100</v>
       </c>
       <c r="F24" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="G24" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H24" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="I24" s="3"/>
-      <c r="J24" s="4" t="s">
+      <c r="I24" s="2"/>
+      <c r="J24" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K24" s="4"/>
+      <c r="K24" s="3"/>
     </row>
     <row r="25" ht="42" spans="1:11">
       <c r="A25" s="19" t="s">
@@ -3199,23 +3221,23 @@
       <c r="D25" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="3" t="s">
         <v>103</v>
       </c>
       <c r="F25" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="G25" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H25" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="I25" s="3"/>
-      <c r="J25" s="4" t="s">
+      <c r="I25" s="2"/>
+      <c r="J25" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K25" s="4"/>
+      <c r="K25" s="3"/>
     </row>
     <row r="26" ht="28" spans="1:11">
       <c r="A26" s="19" t="s">
@@ -3230,21 +3252,21 @@
       <c r="D26" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="3" t="s">
         <v>107</v>
       </c>
       <c r="F26" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="G26" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H26" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="I26" s="3"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="4" t="s">
+      <c r="I26" s="2"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3" t="s">
         <v>110</v>
       </c>
     </row>
@@ -3261,21 +3283,21 @@
       <c r="D27" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="3" t="s">
         <v>112</v>
       </c>
       <c r="F27" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G27" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H27" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="I27" s="3"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="4" t="s">
+      <c r="I27" s="2"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3" t="s">
         <v>114</v>
       </c>
     </row>
@@ -3292,21 +3314,21 @@
       <c r="D28" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="3" t="s">
         <v>116</v>
       </c>
       <c r="F28" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="G28" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H28" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="I28" s="3"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="4"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
     </row>
     <row r="29" ht="28" spans="1:11">
       <c r="A29" s="19" t="s">
@@ -3321,23 +3343,23 @@
       <c r="D29" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="3" t="s">
         <v>119</v>
       </c>
       <c r="F29" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="G29" s="2" t="s">
         <v>61</v>
       </c>
       <c r="H29" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="I29" s="3"/>
-      <c r="J29" s="4" t="s">
+      <c r="I29" s="2"/>
+      <c r="J29" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="K29" s="4"/>
+      <c r="K29" s="3"/>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="20" t="s">
@@ -3352,21 +3374,21 @@
       <c r="D30" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="3" t="s">
         <v>121</v>
       </c>
       <c r="F30" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="G30" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H30" s="16"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="4" t="s">
+      <c r="I30" s="2"/>
+      <c r="J30" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="K30" s="4"/>
+      <c r="K30" s="3"/>
     </row>
     <row r="31" ht="28" spans="1:11">
       <c r="A31" s="20" t="s">
@@ -3381,19 +3403,19 @@
       <c r="D31" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="3" t="s">
         <v>125</v>
       </c>
       <c r="F31" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="G31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H31" s="16"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="4"/>
-      <c r="K31" s="4"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
     </row>
     <row r="32" ht="28" spans="1:11">
       <c r="A32" s="20" t="s">
@@ -3408,19 +3430,19 @@
       <c r="D32" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F32" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="G32" s="2" t="s">
         <v>130</v>
       </c>
       <c r="H32" s="16"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="4"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
     </row>
     <row r="33" ht="28" spans="1:11">
       <c r="A33" s="20" t="s">
@@ -3435,21 +3457,21 @@
       <c r="D33" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E33" s="3" t="s">
         <v>132</v>
       </c>
       <c r="F33" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="G33" s="3" t="s">
+      <c r="G33" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H33" s="16"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="4" t="s">
+      <c r="I33" s="2"/>
+      <c r="J33" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="K33" s="4"/>
+      <c r="K33" s="3"/>
     </row>
     <row r="34" ht="42" spans="1:11">
       <c r="A34" s="20" t="s">
@@ -3464,21 +3486,21 @@
       <c r="D34" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="3" t="s">
         <v>136</v>
       </c>
       <c r="F34" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="G34" s="3" t="s">
+      <c r="G34" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H34" s="16"/>
-      <c r="I34" s="3"/>
-      <c r="J34" s="4" t="s">
+      <c r="I34" s="2"/>
+      <c r="J34" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="K34" s="4" t="s">
+      <c r="K34" s="3" t="s">
         <v>138</v>
       </c>
     </row>
@@ -3495,23 +3517,23 @@
       <c r="D35" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="3" t="s">
         <v>140</v>
       </c>
       <c r="F35" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="G35" s="3" t="s">
+      <c r="G35" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="I35" s="3"/>
-      <c r="J35" s="4" t="s">
+      <c r="I35" s="2"/>
+      <c r="J35" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="K35" s="4"/>
+      <c r="K35" s="3"/>
     </row>
     <row r="36" ht="28" spans="1:11">
       <c r="A36" s="20" t="s">
@@ -3526,21 +3548,21 @@
       <c r="D36" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="3" t="s">
         <v>144</v>
       </c>
       <c r="F36" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="G36" s="3" t="s">
+      <c r="G36" s="2" t="s">
         <v>61</v>
       </c>
       <c r="H36" s="16"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="4" t="s">
+      <c r="I36" s="2"/>
+      <c r="J36" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="K36" s="4"/>
+      <c r="K36" s="3"/>
     </row>
     <row r="37" ht="42" spans="1:11">
       <c r="A37" s="20" t="s">
@@ -3555,19 +3577,19 @@
       <c r="D37" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="E37" s="3" t="s">
         <v>146</v>
       </c>
       <c r="F37" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="G37" s="3" t="s">
+      <c r="G37" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H37" s="16"/>
-      <c r="I37" s="3"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="3"/>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="20" t="s">
@@ -3582,23 +3604,23 @@
       <c r="D38" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E38" s="3" t="s">
         <v>149</v>
       </c>
       <c r="F38" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="G38" s="3" t="s">
+      <c r="G38" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H38" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="I38" s="3"/>
-      <c r="J38" s="4" t="s">
+      <c r="I38" s="2"/>
+      <c r="J38" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="K38" s="4" t="s">
+      <c r="K38" s="3" t="s">
         <v>150</v>
       </c>
     </row>
@@ -3615,23 +3637,23 @@
       <c r="D39" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="E39" s="3" t="s">
         <v>152</v>
       </c>
       <c r="F39" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="G39" s="3" t="s">
+      <c r="G39" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H39" s="16"/>
-      <c r="I39" s="3"/>
-      <c r="J39" s="4" t="s">
+      <c r="I39" s="2"/>
+      <c r="J39" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="K39" s="4"/>
-    </row>
-    <row r="40" ht="70" spans="1:11">
+      <c r="K39" s="3"/>
+    </row>
+    <row r="40" ht="56" spans="1:11">
       <c r="A40" s="20" t="s">
         <v>153</v>
       </c>
@@ -3644,21 +3666,21 @@
       <c r="D40" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="E40" s="3" t="s">
         <v>154</v>
       </c>
       <c r="F40" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="G40" s="3" t="s">
+      <c r="G40" s="2" t="s">
         <v>61</v>
       </c>
       <c r="H40" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="I40" s="3"/>
-      <c r="J40" s="4"/>
-      <c r="K40" s="4" t="s">
+      <c r="I40" s="2"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3" t="s">
         <v>156</v>
       </c>
     </row>
@@ -3675,21 +3697,21 @@
       <c r="D41" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="E41" s="4" t="s">
+      <c r="E41" s="3" t="s">
         <v>158</v>
       </c>
       <c r="F41" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="G41" s="3" t="s">
+      <c r="G41" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H41" s="16"/>
-      <c r="I41" s="3"/>
-      <c r="J41" s="4" t="s">
+      <c r="I41" s="2"/>
+      <c r="J41" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="K41" s="4" t="s">
+      <c r="K41" s="3" t="s">
         <v>159</v>
       </c>
     </row>
@@ -3706,23 +3728,23 @@
       <c r="D42" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="E42" s="3" t="s">
         <v>161</v>
       </c>
       <c r="F42" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="G42" s="3" t="s">
+      <c r="G42" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H42" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="I42" s="3"/>
-      <c r="J42" s="4" t="s">
+      <c r="I42" s="2"/>
+      <c r="J42" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="K42" s="4"/>
+      <c r="K42" s="3"/>
     </row>
     <row r="43" ht="28" spans="1:11">
       <c r="A43" s="21" t="s">
@@ -3737,21 +3759,21 @@
       <c r="D43" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="E43" s="3" t="s">
         <v>164</v>
       </c>
       <c r="F43" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="G43" s="3" t="s">
+      <c r="G43" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H43" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="I43" s="3"/>
-      <c r="J43" s="4"/>
-      <c r="K43" s="4"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="3"/>
+      <c r="K43" s="3"/>
     </row>
     <row r="44" ht="28" spans="1:11">
       <c r="A44" s="21" t="s">
@@ -3766,23 +3788,23 @@
       <c r="D44" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="E44" s="3" t="s">
         <v>167</v>
       </c>
       <c r="F44" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="G44" s="3" t="s">
+      <c r="G44" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H44" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="I44" s="3"/>
-      <c r="J44" s="4" t="s">
+      <c r="I44" s="2"/>
+      <c r="J44" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K44" s="4"/>
+      <c r="K44" s="3"/>
     </row>
     <row r="45" ht="28" spans="1:11">
       <c r="A45" s="21" t="s">
@@ -3797,23 +3819,23 @@
       <c r="D45" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E45" s="4" t="s">
+      <c r="E45" s="3" t="s">
         <v>170</v>
       </c>
       <c r="F45" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="G45" s="3" t="s">
+      <c r="G45" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H45" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="I45" s="3"/>
-      <c r="J45" s="4" t="s">
+      <c r="I45" s="2"/>
+      <c r="J45" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="K45" s="4" t="s">
+      <c r="K45" s="3" t="s">
         <v>172</v>
       </c>
     </row>
@@ -3830,21 +3852,21 @@
       <c r="D46" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="E46" s="3" t="s">
         <v>174</v>
       </c>
       <c r="F46" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="G46" s="3" t="s">
+      <c r="G46" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H46" s="16"/>
-      <c r="I46" s="3"/>
-      <c r="J46" s="4" t="s">
+      <c r="I46" s="2"/>
+      <c r="J46" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="K46" s="4"/>
+      <c r="K46" s="3"/>
     </row>
     <row r="47" ht="42" spans="1:11">
       <c r="A47" s="21" t="s">
@@ -3859,19 +3881,19 @@
       <c r="D47" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="E47" s="3" t="s">
         <v>177</v>
       </c>
       <c r="F47" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="G47" s="3" t="s">
+      <c r="G47" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H47" s="16"/>
-      <c r="I47" s="3"/>
-      <c r="J47" s="4"/>
-      <c r="K47" s="4" t="s">
+      <c r="I47" s="2"/>
+      <c r="J47" s="3"/>
+      <c r="K47" s="3" t="s">
         <v>178</v>
       </c>
     </row>
@@ -3888,23 +3910,23 @@
       <c r="D48" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="E48" s="3" t="s">
         <v>181</v>
       </c>
       <c r="F48" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="G48" s="3" t="s">
+      <c r="G48" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H48" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="I48" s="3"/>
-      <c r="J48" s="4" t="s">
+      <c r="I48" s="2"/>
+      <c r="J48" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="K48" s="4" t="s">
+      <c r="K48" s="3" t="s">
         <v>182</v>
       </c>
     </row>
@@ -3921,21 +3943,21 @@
       <c r="D49" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E49" s="4" t="s">
+      <c r="E49" s="3" t="s">
         <v>184</v>
       </c>
       <c r="F49" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="G49" s="3" t="s">
+      <c r="G49" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H49" s="16"/>
-      <c r="I49" s="3"/>
-      <c r="J49" s="4" t="s">
+      <c r="I49" s="2"/>
+      <c r="J49" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="K49" s="4" t="s">
+      <c r="K49" s="3" t="s">
         <v>186</v>
       </c>
     </row>
@@ -3952,23 +3974,23 @@
       <c r="D50" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E50" s="4" t="s">
+      <c r="E50" s="3" t="s">
         <v>188</v>
       </c>
       <c r="F50" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="G50" s="3" t="s">
+      <c r="G50" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H50" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="I50" s="3"/>
-      <c r="J50" s="4" t="s">
+      <c r="I50" s="2"/>
+      <c r="J50" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K50" s="4"/>
+      <c r="K50" s="3"/>
     </row>
     <row r="51" ht="42" spans="1:11">
       <c r="A51" s="21" t="s">
@@ -3983,19 +4005,19 @@
       <c r="D51" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E51" s="4" t="s">
+      <c r="E51" s="3" t="s">
         <v>190</v>
       </c>
       <c r="F51" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="G51" s="3" t="s">
+      <c r="G51" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H51" s="16"/>
-      <c r="I51" s="3"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="4" t="s">
+      <c r="I51" s="2"/>
+      <c r="J51" s="3"/>
+      <c r="K51" s="3" t="s">
         <v>192</v>
       </c>
     </row>
@@ -4012,19 +4034,19 @@
       <c r="D52" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="E52" s="4" t="s">
+      <c r="E52" s="3" t="s">
         <v>194</v>
       </c>
       <c r="F52" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="G52" s="3" t="s">
+      <c r="G52" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H52" s="16"/>
-      <c r="I52" s="3"/>
-      <c r="J52" s="4"/>
-      <c r="K52" s="4"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="3"/>
+      <c r="K52" s="3"/>
     </row>
     <row r="53" ht="28" spans="1:11">
       <c r="A53" s="21" t="s">
@@ -4039,21 +4061,21 @@
       <c r="D53" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E53" s="4" t="s">
+      <c r="E53" s="3" t="s">
         <v>196</v>
       </c>
       <c r="F53" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="G53" s="3" t="s">
+      <c r="G53" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H53" s="16"/>
-      <c r="I53" s="3"/>
-      <c r="J53" s="4" t="s">
+      <c r="I53" s="2"/>
+      <c r="J53" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="K53" s="4"/>
+      <c r="K53" s="3"/>
     </row>
     <row r="54" ht="28" spans="1:11">
       <c r="A54" s="19" t="s">
@@ -4068,23 +4090,23 @@
       <c r="D54" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E54" s="4" t="s">
+      <c r="E54" s="3" t="s">
         <v>200</v>
       </c>
       <c r="F54" s="15" t="s">
         <v>201</v>
       </c>
-      <c r="G54" s="3" t="s">
+      <c r="G54" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H54" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="I54" s="3"/>
-      <c r="J54" s="4" t="s">
+      <c r="I54" s="2"/>
+      <c r="J54" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K54" s="4"/>
+      <c r="K54" s="3"/>
     </row>
     <row r="55" ht="28" spans="1:11">
       <c r="A55" s="21" t="s">
@@ -4099,23 +4121,23 @@
       <c r="D55" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E55" s="4" t="s">
+      <c r="E55" s="3" t="s">
         <v>203</v>
       </c>
       <c r="F55" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="G55" s="3" t="s">
+      <c r="G55" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H55" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="I55" s="3"/>
-      <c r="J55" s="4" t="s">
+      <c r="I55" s="2"/>
+      <c r="J55" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="K55" s="4" t="s">
+      <c r="K55" s="3" t="s">
         <v>206</v>
       </c>
     </row>
@@ -4132,19 +4154,19 @@
       <c r="D56" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E56" s="4" t="s">
+      <c r="E56" s="3" t="s">
         <v>208</v>
       </c>
       <c r="F56" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="G56" s="3" t="s">
+      <c r="G56" s="2" t="s">
         <v>130</v>
       </c>
       <c r="H56" s="16"/>
-      <c r="I56" s="3"/>
-      <c r="J56" s="4"/>
-      <c r="K56" s="4"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="3"/>
+      <c r="K56" s="3"/>
     </row>
     <row r="57" ht="42" spans="1:11">
       <c r="A57" s="17" t="s">
@@ -4159,21 +4181,21 @@
       <c r="D57" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E57" s="4" t="s">
+      <c r="E57" s="3" t="s">
         <v>211</v>
       </c>
       <c r="F57" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="G57" s="3" t="s">
+      <c r="G57" s="2" t="s">
         <v>61</v>
       </c>
       <c r="H57" s="16"/>
-      <c r="I57" s="3"/>
-      <c r="J57" s="4" t="s">
+      <c r="I57" s="2"/>
+      <c r="J57" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="K57" s="4" t="s">
+      <c r="K57" s="3" t="s">
         <v>213</v>
       </c>
     </row>
@@ -4190,21 +4212,21 @@
       <c r="D58" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E58" s="4" t="s">
+      <c r="E58" s="3" t="s">
         <v>216</v>
       </c>
       <c r="F58" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="G58" s="3" t="s">
+      <c r="G58" s="2" t="s">
         <v>61</v>
       </c>
       <c r="H58" s="16"/>
-      <c r="I58" s="3"/>
-      <c r="J58" s="4" t="s">
+      <c r="I58" s="2"/>
+      <c r="J58" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="K58" s="4"/>
+      <c r="K58" s="3"/>
     </row>
     <row r="59" ht="56" spans="1:11">
       <c r="A59" s="19" t="s">
@@ -4219,23 +4241,23 @@
       <c r="D59" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E59" s="4" t="s">
+      <c r="E59" s="3" t="s">
         <v>220</v>
       </c>
       <c r="F59" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="G59" s="3" t="s">
+      <c r="G59" s="2" t="s">
         <v>61</v>
       </c>
       <c r="H59" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="I59" s="3"/>
-      <c r="J59" s="4" t="s">
+      <c r="I59" s="2"/>
+      <c r="J59" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="K59" s="4"/>
+      <c r="K59" s="3"/>
     </row>
     <row r="60" ht="70" spans="1:11">
       <c r="A60" s="21" t="s">
@@ -4250,21 +4272,21 @@
       <c r="D60" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="E60" s="4" t="s">
+      <c r="E60" s="3" t="s">
         <v>224</v>
       </c>
       <c r="F60" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="G60" s="3" t="s">
+      <c r="G60" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H60" s="16"/>
-      <c r="I60" s="3"/>
-      <c r="J60" s="4" t="s">
+      <c r="I60" s="2"/>
+      <c r="J60" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="K60" s="4"/>
+      <c r="K60" s="3"/>
     </row>
     <row r="61" ht="42" spans="1:11">
       <c r="A61" s="17" t="s">
@@ -4279,23 +4301,23 @@
       <c r="D61" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E61" s="4" t="s">
+      <c r="E61" s="3" t="s">
         <v>227</v>
       </c>
       <c r="F61" s="15" t="s">
         <v>228</v>
       </c>
-      <c r="G61" s="3" t="s">
+      <c r="G61" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H61" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="I61" s="3"/>
-      <c r="J61" s="4" t="s">
+      <c r="I61" s="2"/>
+      <c r="J61" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="K61" s="4"/>
+      <c r="K61" s="3"/>
     </row>
     <row r="62" ht="28" spans="1:11">
       <c r="A62" s="20" t="s">
@@ -4310,21 +4332,21 @@
       <c r="D62" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E62" s="4" t="s">
+      <c r="E62" s="3" t="s">
         <v>231</v>
       </c>
       <c r="F62" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="G62" s="3" t="s">
+      <c r="G62" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H62" s="16"/>
-      <c r="I62" s="3"/>
-      <c r="J62" s="4" t="s">
+      <c r="I62" s="2"/>
+      <c r="J62" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="K62" s="4"/>
+      <c r="K62" s="3"/>
     </row>
     <row r="63" ht="42" spans="1:11">
       <c r="A63" s="19" t="s">
@@ -4339,23 +4361,23 @@
       <c r="D63" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E63" s="4" t="s">
+      <c r="E63" s="3" t="s">
         <v>234</v>
       </c>
       <c r="F63" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="G63" s="3" t="s">
+      <c r="G63" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H63" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="I63" s="3"/>
-      <c r="J63" s="4" t="s">
+      <c r="I63" s="2"/>
+      <c r="J63" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="K63" s="4"/>
+      <c r="K63" s="3"/>
     </row>
     <row r="64" ht="28" spans="1:11">
       <c r="A64" s="19" t="s">
@@ -4370,21 +4392,21 @@
       <c r="D64" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E64" s="4" t="s">
+      <c r="E64" s="3" t="s">
         <v>238</v>
       </c>
       <c r="F64" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="G64" s="3" t="s">
+      <c r="G64" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H64" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="I64" s="3"/>
-      <c r="J64" s="4"/>
-      <c r="K64" s="4"/>
+      <c r="I64" s="2"/>
+      <c r="J64" s="3"/>
+      <c r="K64" s="3"/>
     </row>
     <row r="65" ht="28" spans="1:11">
       <c r="A65" s="22" t="s">
@@ -4399,21 +4421,21 @@
       <c r="D65" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E65" s="4" t="s">
+      <c r="E65" s="3" t="s">
         <v>241</v>
       </c>
       <c r="F65" s="15" t="s">
         <v>242</v>
       </c>
-      <c r="G65" s="3" t="s">
+      <c r="G65" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H65" s="16"/>
-      <c r="I65" s="3"/>
-      <c r="J65" s="4" t="s">
+      <c r="I65" s="2"/>
+      <c r="J65" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="K65" s="4" t="s">
+      <c r="K65" s="3" t="s">
         <v>243</v>
       </c>
     </row>
@@ -4430,23 +4452,23 @@
       <c r="D66" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E66" s="4" t="s">
+      <c r="E66" s="3" t="s">
         <v>245</v>
       </c>
       <c r="F66" s="15" t="s">
         <v>246</v>
       </c>
-      <c r="G66" s="3" t="s">
+      <c r="G66" s="2" t="s">
         <v>247</v>
       </c>
       <c r="H66" s="16" t="s">
         <v>248</v>
       </c>
-      <c r="I66" s="3"/>
-      <c r="J66" s="4" t="s">
+      <c r="I66" s="2"/>
+      <c r="J66" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="K66" s="4" t="s">
+      <c r="K66" s="3" t="s">
         <v>249</v>
       </c>
     </row>
@@ -4463,21 +4485,21 @@
       <c r="D67" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E67" s="4" t="s">
+      <c r="E67" s="3" t="s">
         <v>251</v>
       </c>
       <c r="F67" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="G67" s="3" t="s">
+      <c r="G67" s="2" t="s">
         <v>247</v>
       </c>
       <c r="H67" s="16"/>
-      <c r="I67" s="3"/>
-      <c r="J67" s="4" t="s">
+      <c r="I67" s="2"/>
+      <c r="J67" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="K67" s="4" t="s">
+      <c r="K67" s="3" t="s">
         <v>243</v>
       </c>
     </row>
@@ -4494,19 +4516,19 @@
       <c r="D68" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E68" s="4" t="s">
+      <c r="E68" s="3" t="s">
         <v>254</v>
       </c>
       <c r="F68" s="15" t="s">
         <v>255</v>
       </c>
-      <c r="G68" s="3" t="s">
+      <c r="G68" s="2" t="s">
         <v>130</v>
       </c>
       <c r="H68" s="16"/>
-      <c r="I68" s="3"/>
-      <c r="J68" s="4"/>
-      <c r="K68" s="4"/>
+      <c r="I68" s="2"/>
+      <c r="J68" s="3"/>
+      <c r="K68" s="3"/>
     </row>
     <row r="69" ht="28" spans="1:11">
       <c r="A69" s="17" t="s">
@@ -4521,21 +4543,21 @@
       <c r="D69" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E69" s="4" t="s">
+      <c r="E69" s="3" t="s">
         <v>257</v>
       </c>
       <c r="F69" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="G69" s="3" t="s">
+      <c r="G69" s="2" t="s">
         <v>61</v>
       </c>
       <c r="H69" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="I69" s="3"/>
-      <c r="J69" s="4"/>
-      <c r="K69" s="4"/>
+      <c r="I69" s="2"/>
+      <c r="J69" s="3"/>
+      <c r="K69" s="3"/>
     </row>
     <row r="70" ht="42" spans="1:11">
       <c r="A70" s="19" t="s">
@@ -4550,21 +4572,21 @@
       <c r="D70" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E70" s="4" t="s">
+      <c r="E70" s="3" t="s">
         <v>259</v>
       </c>
       <c r="F70" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="G70" s="3" t="s">
+      <c r="G70" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H70" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="I70" s="3"/>
-      <c r="J70" s="4"/>
-      <c r="K70" s="4" t="s">
+      <c r="I70" s="2"/>
+      <c r="J70" s="3"/>
+      <c r="K70" s="3" t="s">
         <v>260</v>
       </c>
     </row>
@@ -4581,21 +4603,21 @@
       <c r="D71" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="E71" s="4" t="s">
+      <c r="E71" s="3" t="s">
         <v>262</v>
       </c>
       <c r="F71" s="15" t="s">
         <v>263</v>
       </c>
-      <c r="G71" s="3" t="s">
+      <c r="G71" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H71" s="16"/>
-      <c r="I71" s="3"/>
-      <c r="J71" s="4" t="s">
+      <c r="I71" s="2"/>
+      <c r="J71" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="K71" s="4" t="s">
+      <c r="K71" s="3" t="s">
         <v>264</v>
       </c>
     </row>
@@ -4603,63 +4625,63 @@
       <c r="A72" s="19" t="s">
         <v>265</v>
       </c>
-      <c r="B72" s="23">
+      <c r="B72" s="14">
         <v>1</v>
       </c>
-      <c r="C72" s="23" t="s">
+      <c r="C72" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D72" s="23" t="s">
+      <c r="D72" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="E72" s="5" t="s">
+      <c r="E72" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="F72" s="5" t="s">
+      <c r="F72" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="G72" s="3" t="s">
+      <c r="G72" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>82</v>
       </c>
       <c r="I72" s="2"/>
-      <c r="J72" s="5" t="s">
+      <c r="J72" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K72" s="24" t="s">
+      <c r="K72" s="23" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="73" ht="43.5" spans="1:11">
-      <c r="A73" s="25" t="s">
+      <c r="A73" s="24" t="s">
         <v>269</v>
       </c>
-      <c r="B73" s="23">
+      <c r="B73" s="14">
         <v>1</v>
       </c>
-      <c r="C73" s="23" t="s">
+      <c r="C73" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D73" s="23" t="s">
+      <c r="D73" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E73" s="5" t="s">
+      <c r="E73" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="F73" s="5" t="s">
+      <c r="F73" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="G73" s="3" t="s">
+      <c r="G73" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>142</v>
       </c>
       <c r="I73" s="2"/>
-      <c r="J73" s="5"/>
-      <c r="K73" s="26" t="s">
+      <c r="J73" s="3"/>
+      <c r="K73" s="25" t="s">
         <v>272</v>
       </c>
     </row>
@@ -4667,61 +4689,61 @@
       <c r="A74" s="19" t="s">
         <v>273</v>
       </c>
-      <c r="B74" s="23">
+      <c r="B74" s="14">
         <v>1</v>
       </c>
-      <c r="C74" s="23" t="s">
+      <c r="C74" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D74" s="23" t="s">
+      <c r="D74" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E74" s="5" t="s">
+      <c r="E74" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="F74" s="5" t="s">
+      <c r="F74" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="G74" s="3" t="s">
+      <c r="G74" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H74" s="2"/>
       <c r="I74" s="2"/>
-      <c r="J74" s="5" t="s">
+      <c r="J74" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="K74" s="24" t="s">
+      <c r="K74" s="23" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="75" ht="42" spans="1:11">
-      <c r="A75" s="25" t="s">
+      <c r="A75" s="24" t="s">
         <v>278</v>
       </c>
-      <c r="B75" s="23">
+      <c r="B75" s="14">
         <v>1</v>
       </c>
-      <c r="C75" s="23" t="s">
+      <c r="C75" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="D75" s="23" t="s">
+      <c r="D75" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E75" s="5" t="s">
+      <c r="E75" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="F75" s="5" t="s">
+      <c r="F75" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G75" s="3" t="s">
+      <c r="G75" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>142</v>
       </c>
       <c r="I75" s="2"/>
-      <c r="J75" s="5"/>
-      <c r="K75" s="5" t="s">
+      <c r="J75" s="3"/>
+      <c r="K75" s="3" t="s">
         <v>280</v>
       </c>
     </row>
@@ -4729,201 +4751,213 @@
       <c r="A76" s="20" t="s">
         <v>281</v>
       </c>
-      <c r="B76" s="23">
+      <c r="B76" s="14">
         <v>1</v>
       </c>
-      <c r="C76" s="23" t="s">
+      <c r="C76" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D76" s="23" t="s">
+      <c r="D76" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E76" s="5" t="s">
+      <c r="E76" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="F76" s="5" t="s">
+      <c r="F76" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="G76" s="3" t="s">
+      <c r="G76" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H76" s="2"/>
       <c r="I76" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J76" s="5" t="s">
+      <c r="J76" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="K76" s="5"/>
+      <c r="K76" s="3"/>
     </row>
     <row r="77" ht="28" spans="1:11">
       <c r="A77" s="19" t="s">
         <v>284</v>
       </c>
-      <c r="B77" s="23">
+      <c r="B77" s="14">
         <v>1</v>
       </c>
-      <c r="C77" s="23" t="s">
+      <c r="C77" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D77" s="23" t="s">
+      <c r="D77" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="E77" s="5" t="s">
+      <c r="E77" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="F77" s="5" t="s">
+      <c r="F77" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G77" s="3" t="s">
+      <c r="G77" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>82</v>
       </c>
       <c r="I77" s="2"/>
-      <c r="J77" s="5" t="s">
+      <c r="J77" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="K77" s="5"/>
+      <c r="K77" s="3"/>
     </row>
     <row r="78" spans="1:11">
       <c r="A78" s="17" t="s">
         <v>287</v>
       </c>
-      <c r="B78" s="23">
+      <c r="B78" s="14">
         <v>1</v>
       </c>
-      <c r="C78" s="23" t="s">
+      <c r="C78" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D78" s="23" t="s">
+      <c r="D78" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="E78" s="5" t="s">
+      <c r="E78" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="F78" s="5" t="s">
+      <c r="F78" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G78" s="3" t="s">
+      <c r="G78" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H78" s="2"/>
       <c r="I78" s="2"/>
-      <c r="J78" s="5" t="s">
+      <c r="J78" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="K78" s="5"/>
+      <c r="K78" s="3"/>
     </row>
     <row r="79" spans="1:11">
       <c r="A79" s="17" t="s">
         <v>289</v>
       </c>
-      <c r="B79" s="23">
+      <c r="B79" s="14">
         <v>2</v>
       </c>
-      <c r="C79" s="23" t="s">
+      <c r="C79" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D79" s="23" t="s">
+      <c r="D79" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="E79" s="5" t="s">
+      <c r="E79" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="F79" s="5" t="s">
+      <c r="F79" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G79" s="3" t="s">
+      <c r="G79" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H79" s="2"/>
       <c r="I79" s="2"/>
-      <c r="J79" s="5" t="s">
+      <c r="J79" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="K79" s="5"/>
+      <c r="K79" s="3"/>
     </row>
     <row r="80" spans="1:11">
-      <c r="A80" s="23"/>
-      <c r="B80" s="23"/>
-      <c r="C80" s="23" t="s">
+      <c r="A80" s="14"/>
+      <c r="B80" s="14"/>
+      <c r="C80" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D80" s="23" t="s">
+      <c r="D80" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="E80" s="5"/>
-      <c r="F80" s="5"/>
-      <c r="G80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3"/>
+      <c r="G80" s="2"/>
       <c r="H80" s="2"/>
       <c r="I80" s="2"/>
-      <c r="J80" s="5"/>
-      <c r="K80" s="5"/>
+      <c r="J80" s="3"/>
+      <c r="K80" s="3"/>
     </row>
     <row r="81" ht="42" spans="1:11">
       <c r="A81" s="20" t="s">
         <v>291</v>
       </c>
-      <c r="B81" s="23">
+      <c r="B81" s="14">
         <v>1</v>
       </c>
-      <c r="C81" s="23" t="s">
+      <c r="C81" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D81" s="23" t="s">
+      <c r="D81" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E81" s="5" t="s">
+      <c r="E81" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="F81" s="5" t="s">
+      <c r="F81" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="G81" s="3" t="s">
+      <c r="G81" s="2" t="s">
         <v>130</v>
       </c>
       <c r="H81" s="2"/>
       <c r="I81" s="2"/>
-      <c r="J81" s="5" t="s">
+      <c r="J81" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="K81" s="5"/>
-    </row>
-    <row r="82" spans="1:11">
-      <c r="A82" s="23"/>
-      <c r="B82" s="23"/>
-      <c r="C82" s="23" t="s">
+      <c r="K81" s="3"/>
+    </row>
+    <row r="82" ht="28" spans="1:11">
+      <c r="A82" s="17" t="s">
+        <v>294</v>
+      </c>
+      <c r="B82" s="14">
+        <v>3</v>
+      </c>
+      <c r="C82" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D82" s="23" t="s">
+      <c r="D82" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E82" s="5"/>
-      <c r="F82" s="5"/>
-      <c r="G82" s="3"/>
-      <c r="H82" s="2"/>
+      <c r="E82" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>204</v>
+      </c>
       <c r="I82" s="2"/>
-      <c r="J82" s="5"/>
-      <c r="K82" s="5"/>
+      <c r="J82" s="3"/>
+      <c r="K82" s="3"/>
     </row>
     <row r="83" spans="1:11">
-      <c r="A83" s="23"/>
-      <c r="B83" s="23"/>
-      <c r="C83" s="23" t="s">
+      <c r="A83" s="14"/>
+      <c r="B83" s="14"/>
+      <c r="C83" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D83" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E83" s="5"/>
-      <c r="F83" s="5"/>
-      <c r="G83" s="3"/>
+      <c r="D83" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3"/>
+      <c r="G83" s="2"/>
       <c r="H83" s="2"/>
       <c r="I83" s="2"/>
-      <c r="J83" s="5"/>
-      <c r="K83" s="5"/>
+      <c r="J83" s="3"/>
+      <c r="K83" s="3"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K83" etc:filterBottomFollowUsedRange="0">
@@ -4996,10 +5030,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C77 C78:C83 C84:C1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576">
       <formula1>"初始Basic,普通Common,罕见UnCommon,稀有Rare,先古Ancient,临时生成Token"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D77 D78:D80 D81:D83 D84:D1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
       <formula1>"攻击,技能,能力"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G85">
@@ -5015,7 +5049,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="16.0909090909091" customWidth="1"/>
@@ -5024,473 +5058,473 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="B1" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="E1" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="4"/>
+      <c r="B2" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="F2" s="3"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="B3" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="4"/>
+      <c r="D3" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="3"/>
     </row>
     <row r="4" ht="42" spans="1:6">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="4" t="s">
-        <v>303</v>
+      <c r="E4" s="2"/>
+      <c r="F4" s="3" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="5" ht="56" spans="1:6">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="3" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="6" ht="28" spans="1:6">
+      <c r="A6" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="3" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="7" ht="42" spans="1:6">
+      <c r="A7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="8" ht="28" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="3" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" ht="28" spans="1:6">
+      <c r="A10" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="3"/>
+    </row>
+    <row r="11" ht="56" spans="1:6">
+      <c r="A11" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="12" ht="56" spans="1:6">
+      <c r="A12" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="3"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" s="3"/>
+    </row>
+    <row r="15" ht="28" spans="1:6">
+      <c r="A15" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="16" ht="28" spans="1:6">
+      <c r="A16" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="4" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="6" ht="28" spans="1:6">
-      <c r="A6" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="4" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="7" ht="42" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="4" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="8" ht="28" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="4" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="4"/>
-    </row>
-    <row r="10" ht="28" spans="1:6">
-      <c r="A10" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="4"/>
-    </row>
-    <row r="11" ht="56" spans="1:6">
-      <c r="A11" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="12" ht="56" spans="1:6">
-      <c r="A12" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="4" t="s">
+      <c r="E16" s="2" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="4"/>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="4"/>
-    </row>
-    <row r="15" ht="28" spans="1:6">
-      <c r="A15" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="4" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="16" ht="28" spans="1:6">
-      <c r="A16" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D16" s="3" t="s">
+      <c r="F16" s="3" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="F17" s="4"/>
+      <c r="D17" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="F17" s="3"/>
     </row>
     <row r="18" ht="28" spans="1:6">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="4"/>
+      <c r="B18" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" s="3"/>
     </row>
     <row r="19" ht="28" spans="1:6">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="F19" s="4"/>
+      <c r="B19" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="F19" s="3"/>
     </row>
     <row r="20" ht="28" spans="1:6">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D20" s="3" t="s">
+      <c r="B20" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="4" t="s">
-        <v>329</v>
+      <c r="D20" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" s="3" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="4"/>
+      <c r="A21" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" s="3"/>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="4"/>
+      <c r="B22" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" s="3"/>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D23" s="3" t="s">
+      <c r="B23" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="4"/>
+      <c r="D23" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" s="3"/>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>336</v>
+      <c r="B24" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="25" ht="28" spans="1:6">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="4"/>
+      <c r="B25" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" s="3"/>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="4"/>
+      <c r="B26" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" s="3"/>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2" t="s">
         <v>278</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E27" s="2"/>
-      <c r="F27" s="5" t="s">
-        <v>340</v>
+      <c r="F27" s="3" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="28" ht="70" spans="1:6">
@@ -5498,40 +5532,56 @@
         <v>287</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>342</v>
+        <v>318</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="29" ht="42" spans="1:6">
       <c r="A29" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>343</v>
+      <c r="B29" s="3" t="s">
+        <v>346</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>344</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E30" s="4"/>
+      <c r="F30" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5555,10 +5605,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -5582,32 +5632,32 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5641,7 +5691,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -5649,7 +5699,7 @@
         <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -5657,7 +5707,7 @@
         <v>204</v>
       </c>
       <c r="B3" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="4" ht="112" spans="1:2">
@@ -5665,7 +5715,7 @@
         <v>82</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -5673,7 +5723,7 @@
         <v>91</v>
       </c>
       <c r="B5" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -5681,7 +5731,7 @@
         <v>109</v>
       </c>
       <c r="B6" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -5702,31 +5752,31 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="2" ht="28" spans="1:2">
       <c r="A2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="3" ht="28" spans="1:2">
       <c r="A3" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
   </sheetData>

--- a/docs/设计文档.xlsx
+++ b/docs/设计文档.xlsx
@@ -15,7 +15,7 @@
     <sheet name="草稿" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">卡牌!$A$1:$K$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">卡牌!$A$1:$K$90</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="381">
   <si>
     <t>名称</t>
   </si>
@@ -281,7 +281,7 @@
 每回合首次触发叠加效果时，抽2张牌。</t>
   </si>
   <si>
-    <t>获得保留</t>
+    <t>量子叠加层数+1，抽牌数+1</t>
   </si>
   <si>
     <t>触发叠加效果可以由SeleeHook实现</t>
@@ -393,6 +393,9 @@
   </si>
   <si>
     <t>进入星环爆发状态</t>
+  </si>
+  <si>
+    <t>获得保留</t>
   </si>
   <si>
     <t>星环爆发，消耗</t>
@@ -1097,6 +1100,49 @@
   </si>
   <si>
     <t>基础伤害+10</t>
+  </si>
+  <si>
+    <t>永恒=一瞬</t>
+  </si>
+  <si>
+    <t>造成10点伤害
+获得2层量子叠加
+施加2层量子坍缩</t>
+  </si>
+  <si>
+    <t>基础伤害+4，量子叠加层数+1，量子坍缩层数+1</t>
+  </si>
+  <si>
+    <t>固有，消耗</t>
+  </si>
+  <si>
+    <t>量子叠加，量子坍缩</t>
+  </si>
+  <si>
+    <t>罪罚两断之刃</t>
+  </si>
+  <si>
+    <t>造成14点伤害
+目标持有量子坍缩状态时，获得1点能量和1层量子叠加</t>
+  </si>
+  <si>
+    <t>基础伤害+6</t>
+  </si>
+  <si>
+    <t>量子坍缩，能量，量子叠加</t>
+  </si>
+  <si>
+    <t>X-10实验</t>
+  </si>
+  <si>
+    <t>打出抽牌堆的2张牌
+回合开始时，少抽1张牌</t>
+  </si>
+  <si>
+    <t>打出牌数+1</t>
+  </si>
+  <si>
+    <t>固有</t>
   </si>
   <si>
     <t>说明</t>
@@ -1499,7 +1545,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1545,12 +1591,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1914,7 +1954,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="4">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
@@ -1938,16 +1978,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="7">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="8">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="7">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="9">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="9">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="10">
@@ -1956,85 +1996,85 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="11">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="36" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="38" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="39" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="40" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="39" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2111,11 +2151,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2197,9 +2237,9 @@
     <mruColors>
       <color rgb="00F9CB95"/>
       <color rgb="00D2A9F5"/>
-      <color rgb="00FFFE61"/>
       <color rgb="00BDEFE9"/>
       <color rgb="00BC7EF0"/>
+      <color rgb="00FFFE61"/>
     </mruColors>
   </colors>
   <extLst>
@@ -2460,7 +2500,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K83"/>
+  <dimension ref="A1:K90"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="19.0909090909091" style="7" customWidth="1"/>
@@ -3287,23 +3327,23 @@
         <v>112</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I27" s="2"/>
       <c r="J27" s="3"/>
       <c r="K27" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="19" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B28" s="14">
         <v>1</v>
@@ -3315,10 +3355,10 @@
         <v>55</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>22</v>
@@ -3332,7 +3372,7 @@
     </row>
     <row r="29" ht="28" spans="1:11">
       <c r="A29" s="19" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B29" s="14">
         <v>2</v>
@@ -3344,7 +3384,7 @@
         <v>13</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F29" s="15" t="s">
         <v>86</v>
@@ -3363,7 +3403,7 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="20" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B30" s="14">
         <v>1</v>
@@ -3375,10 +3415,10 @@
         <v>19</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>22</v>
@@ -3386,13 +3426,13 @@
       <c r="H30" s="16"/>
       <c r="I30" s="2"/>
       <c r="J30" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K30" s="3"/>
     </row>
     <row r="31" ht="28" spans="1:11">
       <c r="A31" s="20" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B31" s="14">
         <v>1</v>
@@ -3404,10 +3444,10 @@
         <v>19</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F31" s="15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>22</v>
@@ -3419,7 +3459,7 @@
     </row>
     <row r="32" ht="28" spans="1:11">
       <c r="A32" s="20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B32" s="14">
         <v>1</v>
@@ -3431,13 +3471,13 @@
         <v>13</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F32" s="15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H32" s="16"/>
       <c r="I32" s="2"/>
@@ -3446,7 +3486,7 @@
     </row>
     <row r="33" ht="28" spans="1:11">
       <c r="A33" s="20" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B33" s="14">
         <v>1</v>
@@ -3458,10 +3498,10 @@
         <v>19</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F33" s="15" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>16</v>
@@ -3469,13 +3509,13 @@
       <c r="H33" s="16"/>
       <c r="I33" s="2"/>
       <c r="J33" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K33" s="3"/>
     </row>
     <row r="34" ht="42" spans="1:11">
       <c r="A34" s="20" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B34" s="14">
         <v>1</v>
@@ -3487,7 +3527,7 @@
         <v>55</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F34" s="15" t="s">
         <v>57</v>
@@ -3498,15 +3538,15 @@
       <c r="H34" s="16"/>
       <c r="I34" s="2"/>
       <c r="J34" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="20" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B35" s="14">
         <v>1</v>
@@ -3518,26 +3558,26 @@
         <v>19</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F35" s="15" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="16" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I35" s="2"/>
       <c r="J35" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K35" s="3"/>
     </row>
     <row r="36" ht="28" spans="1:11">
       <c r="A36" s="20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B36" s="14">
         <v>1</v>
@@ -3549,10 +3589,10 @@
         <v>13</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F36" s="15" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>61</v>
@@ -3560,13 +3600,13 @@
       <c r="H36" s="16"/>
       <c r="I36" s="2"/>
       <c r="J36" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K36" s="3"/>
     </row>
     <row r="37" ht="42" spans="1:11">
       <c r="A37" s="20" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B37" s="14">
         <v>0</v>
@@ -3578,10 +3618,10 @@
         <v>19</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F37" s="15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>22</v>
@@ -3593,7 +3633,7 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="20" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B38" s="14">
         <v>2</v>
@@ -3605,28 +3645,28 @@
         <v>19</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F38" s="15" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H38" s="16" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I38" s="2"/>
       <c r="J38" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="20" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B39" s="14">
         <v>1</v>
@@ -3638,10 +3678,10 @@
         <v>19</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F39" s="15" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>16</v>
@@ -3649,13 +3689,13 @@
       <c r="H39" s="16"/>
       <c r="I39" s="2"/>
       <c r="J39" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K39" s="3"/>
     </row>
     <row r="40" ht="56" spans="1:11">
       <c r="A40" s="20" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B40" s="14">
         <v>2</v>
@@ -3667,26 +3707,26 @@
         <v>13</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F40" s="15" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>61</v>
       </c>
       <c r="H40" s="16" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I40" s="2"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="41" ht="56" spans="1:11">
       <c r="A41" s="20" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B41" s="14">
         <v>2</v>
@@ -3698,7 +3738,7 @@
         <v>55</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F41" s="15" t="s">
         <v>34</v>
@@ -3709,15 +3749,15 @@
       <c r="H41" s="16"/>
       <c r="I41" s="2"/>
       <c r="J41" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="42" ht="28" spans="1:11">
       <c r="A42" s="21" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B42" s="14">
         <v>1</v>
@@ -3729,16 +3769,16 @@
         <v>19</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F42" s="15" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H42" s="16" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I42" s="2"/>
       <c r="J42" s="3" t="s">
@@ -3748,7 +3788,7 @@
     </row>
     <row r="43" ht="28" spans="1:11">
       <c r="A43" s="21" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B43" s="14">
         <v>1</v>
@@ -3760,10 +3800,10 @@
         <v>13</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F43" s="15" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>16</v>
@@ -3777,7 +3817,7 @@
     </row>
     <row r="44" ht="28" spans="1:11">
       <c r="A44" s="21" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B44" s="14">
         <v>1</v>
@@ -3789,10 +3829,10 @@
         <v>19</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F44" s="15" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>22</v>
@@ -3808,7 +3848,7 @@
     </row>
     <row r="45" ht="28" spans="1:11">
       <c r="A45" s="21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B45" s="14">
         <v>1</v>
@@ -3820,10 +3860,10 @@
         <v>19</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F45" s="15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>22</v>
@@ -3833,15 +3873,15 @@
       </c>
       <c r="I45" s="2"/>
       <c r="J45" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="46" ht="28" spans="1:11">
       <c r="A46" s="21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B46" s="14">
         <v>1</v>
@@ -3853,7 +3893,7 @@
         <v>19</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F46" s="15" t="s">
         <v>46</v>
@@ -3864,13 +3904,13 @@
       <c r="H46" s="16"/>
       <c r="I46" s="2"/>
       <c r="J46" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K46" s="3"/>
     </row>
     <row r="47" ht="42" spans="1:11">
       <c r="A47" s="21" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B47" s="14">
         <v>1</v>
@@ -3882,10 +3922,10 @@
         <v>19</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F47" s="15" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>22</v>
@@ -3894,45 +3934,45 @@
       <c r="I47" s="2"/>
       <c r="J47" s="3"/>
       <c r="K47" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="48" spans="1:11">
       <c r="A48" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B48" s="14">
         <v>0</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D48" s="14" t="s">
         <v>19</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F48" s="15" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H48" s="16" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I48" s="2"/>
       <c r="J48" s="3" t="s">
         <v>35</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="21" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B49" s="14">
         <v>1</v>
@@ -3944,10 +3984,10 @@
         <v>19</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F49" s="15" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>22</v>
@@ -3955,15 +3995,15 @@
       <c r="H49" s="16"/>
       <c r="I49" s="2"/>
       <c r="J49" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="50" ht="28" spans="1:11">
       <c r="A50" s="21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B50" s="14">
         <v>1</v>
@@ -3975,7 +4015,7 @@
         <v>19</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F50" s="15" t="s">
         <v>34</v>
@@ -3984,7 +4024,7 @@
         <v>22</v>
       </c>
       <c r="H50" s="16" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I50" s="2"/>
       <c r="J50" s="3" t="s">
@@ -3994,7 +4034,7 @@
     </row>
     <row r="51" ht="42" spans="1:11">
       <c r="A51" s="21" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B51" s="14">
         <v>1</v>
@@ -4006,10 +4046,10 @@
         <v>19</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F51" s="15" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>22</v>
@@ -4018,12 +4058,12 @@
       <c r="I51" s="2"/>
       <c r="J51" s="3"/>
       <c r="K51" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="52" ht="28" spans="1:11">
       <c r="A52" s="21" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B52" s="14">
         <v>1</v>
@@ -4035,7 +4075,7 @@
         <v>55</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F52" s="15" t="s">
         <v>74</v>
@@ -4050,7 +4090,7 @@
     </row>
     <row r="53" ht="28" spans="1:11">
       <c r="A53" s="21" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B53" s="14">
         <v>1</v>
@@ -4062,10 +4102,10 @@
         <v>19</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F53" s="15" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>22</v>
@@ -4073,13 +4113,13 @@
       <c r="H53" s="16"/>
       <c r="I53" s="2"/>
       <c r="J53" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K53" s="3"/>
     </row>
     <row r="54" ht="28" spans="1:11">
       <c r="A54" s="19" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B54" s="14">
         <v>0</v>
@@ -4091,10 +4131,10 @@
         <v>19</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F54" s="15" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>22</v>
@@ -4110,7 +4150,7 @@
     </row>
     <row r="55" ht="28" spans="1:11">
       <c r="A55" s="21" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B55" s="14">
         <v>0</v>
@@ -4122,28 +4162,28 @@
         <v>19</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F55" s="15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H55" s="16" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I55" s="2"/>
       <c r="J55" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="56" ht="42" spans="1:11">
       <c r="A56" s="21" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B56" s="14">
         <v>1</v>
@@ -4155,13 +4195,13 @@
         <v>13</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F56" s="15" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H56" s="16"/>
       <c r="I56" s="2"/>
@@ -4170,7 +4210,7 @@
     </row>
     <row r="57" ht="42" spans="1:11">
       <c r="A57" s="17" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B57" s="14">
         <v>1</v>
@@ -4182,10 +4222,10 @@
         <v>13</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F57" s="15" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>61</v>
@@ -4196,15 +4236,15 @@
         <v>35</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="58" ht="28" spans="1:11">
       <c r="A58" s="20" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B58" s="14" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C58" s="14" t="s">
         <v>51</v>
@@ -4213,10 +4253,10 @@
         <v>19</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F58" s="15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>61</v>
@@ -4224,13 +4264,13 @@
       <c r="H58" s="16"/>
       <c r="I58" s="2"/>
       <c r="J58" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K58" s="3"/>
     </row>
     <row r="59" ht="56" spans="1:11">
       <c r="A59" s="19" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B59" s="14">
         <v>0</v>
@@ -4242,10 +4282,10 @@
         <v>13</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F59" s="15" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>61</v>
@@ -4255,13 +4295,13 @@
       </c>
       <c r="I59" s="2"/>
       <c r="J59" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K59" s="3"/>
     </row>
     <row r="60" ht="70" spans="1:11">
       <c r="A60" s="21" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B60" s="14">
         <v>0</v>
@@ -4273,7 +4313,7 @@
         <v>55</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F60" s="15" t="s">
         <v>57</v>
@@ -4284,13 +4324,13 @@
       <c r="H60" s="16"/>
       <c r="I60" s="2"/>
       <c r="J60" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K60" s="3"/>
     </row>
     <row r="61" ht="42" spans="1:11">
       <c r="A61" s="17" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B61" s="14">
         <v>1</v>
@@ -4302,10 +4342,10 @@
         <v>13</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F61" s="15" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>16</v>
@@ -4315,13 +4355,13 @@
       </c>
       <c r="I61" s="2"/>
       <c r="J61" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K61" s="3"/>
     </row>
     <row r="62" ht="28" spans="1:11">
       <c r="A62" s="20" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B62" s="14">
         <v>0</v>
@@ -4333,10 +4373,10 @@
         <v>19</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F62" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>22</v>
@@ -4344,13 +4384,13 @@
       <c r="H62" s="16"/>
       <c r="I62" s="2"/>
       <c r="J62" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K62" s="3"/>
     </row>
     <row r="63" ht="42" spans="1:11">
       <c r="A63" s="19" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B63" s="14">
         <v>0</v>
@@ -4362,10 +4402,10 @@
         <v>19</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F63" s="15" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>22</v>
@@ -4375,13 +4415,13 @@
       </c>
       <c r="I63" s="2"/>
       <c r="J63" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K63" s="3"/>
     </row>
     <row r="64" ht="28" spans="1:11">
       <c r="A64" s="19" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B64" s="14">
         <v>0</v>
@@ -4393,10 +4433,10 @@
         <v>13</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F64" s="15" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>22</v>
@@ -4410,7 +4450,7 @@
     </row>
     <row r="65" ht="28" spans="1:11">
       <c r="A65" s="22" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B65" s="14">
         <v>0</v>
@@ -4422,10 +4462,10 @@
         <v>19</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F65" s="15" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>16</v>
@@ -4436,12 +4476,12 @@
         <v>35</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="66" ht="42" spans="1:11">
       <c r="A66" s="22" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B66" s="14">
         <v>1</v>
@@ -4453,28 +4493,28 @@
         <v>19</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F66" s="15" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H66" s="16" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I66" s="2"/>
       <c r="J66" s="3" t="s">
         <v>95</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="67" ht="56" spans="1:11">
       <c r="A67" s="22" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B67" s="14">
         <v>1</v>
@@ -4486,29 +4526,29 @@
         <v>19</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F67" s="15" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H67" s="16"/>
       <c r="I67" s="2"/>
       <c r="J67" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="68" ht="28" spans="1:11">
       <c r="A68" s="19" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B68" s="14" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C68" s="14" t="s">
         <v>51</v>
@@ -4517,13 +4557,13 @@
         <v>13</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F68" s="15" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H68" s="16"/>
       <c r="I68" s="2"/>
@@ -4532,7 +4572,7 @@
     </row>
     <row r="69" ht="28" spans="1:11">
       <c r="A69" s="17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B69" s="14">
         <v>1</v>
@@ -4544,7 +4584,7 @@
         <v>13</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F69" s="15" t="s">
         <v>15</v>
@@ -4561,7 +4601,7 @@
     </row>
     <row r="70" ht="42" spans="1:11">
       <c r="A70" s="19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B70" s="14">
         <v>3</v>
@@ -4573,10 +4613,10 @@
         <v>13</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F70" s="15" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>16</v>
@@ -4587,12 +4627,12 @@
       <c r="I70" s="2"/>
       <c r="J70" s="3"/>
       <c r="K70" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="71" ht="42" spans="1:11">
       <c r="A71" s="20" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B71" s="14">
         <v>1</v>
@@ -4604,10 +4644,10 @@
         <v>55</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F71" s="15" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>22</v>
@@ -4615,15 +4655,15 @@
       <c r="H71" s="16"/>
       <c r="I71" s="2"/>
       <c r="J71" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="72" ht="43.5" spans="1:11">
       <c r="A72" s="19" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B72" s="14">
         <v>1</v>
@@ -4635,10 +4675,10 @@
         <v>55</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>22</v>
@@ -4651,12 +4691,12 @@
         <v>91</v>
       </c>
       <c r="K72" s="23" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="73" ht="43.5" spans="1:11">
-      <c r="A73" s="24" t="s">
-        <v>269</v>
+      <c r="A73" s="21" t="s">
+        <v>270</v>
       </c>
       <c r="B73" s="14">
         <v>1</v>
@@ -4668,26 +4708,26 @@
         <v>19</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I73" s="2"/>
       <c r="J73" s="3"/>
-      <c r="K73" s="25" t="s">
-        <v>272</v>
+      <c r="K73" s="24" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="74" ht="58" spans="1:11">
       <c r="A74" s="19" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B74" s="14">
         <v>1</v>
@@ -4699,10 +4739,10 @@
         <v>19</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>22</v>
@@ -4710,15 +4750,15 @@
       <c r="H74" s="2"/>
       <c r="I74" s="2"/>
       <c r="J74" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K74" s="23" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="75" ht="42" spans="1:11">
-      <c r="A75" s="24" t="s">
-        <v>278</v>
+      <c r="A75" s="21" t="s">
+        <v>279</v>
       </c>
       <c r="B75" s="14">
         <v>1</v>
@@ -4730,7 +4770,7 @@
         <v>19</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>34</v>
@@ -4739,17 +4779,17 @@
         <v>16</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I75" s="2"/>
       <c r="J75" s="3"/>
       <c r="K75" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="76" ht="28" spans="1:11">
       <c r="A76" s="20" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B76" s="14">
         <v>1</v>
@@ -4761,10 +4801,10 @@
         <v>13</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>16</v>
@@ -4774,13 +4814,13 @@
         <v>11</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K76" s="3"/>
     </row>
     <row r="77" ht="28" spans="1:11">
       <c r="A77" s="19" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B77" s="14">
         <v>1</v>
@@ -4792,7 +4832,7 @@
         <v>55</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>34</v>
@@ -4805,13 +4845,13 @@
       </c>
       <c r="I77" s="2"/>
       <c r="J77" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K77" s="3"/>
     </row>
     <row r="78" spans="1:11">
       <c r="A78" s="17" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B78" s="14">
         <v>1</v>
@@ -4823,7 +4863,7 @@
         <v>55</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>34</v>
@@ -4840,7 +4880,7 @@
     </row>
     <row r="79" spans="1:11">
       <c r="A79" s="17" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B79" s="14">
         <v>2</v>
@@ -4852,7 +4892,7 @@
         <v>55</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>34</v>
@@ -4886,7 +4926,7 @@
     </row>
     <row r="81" ht="42" spans="1:11">
       <c r="A81" s="20" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B81" s="14">
         <v>1</v>
@@ -4898,24 +4938,24 @@
         <v>13</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H81" s="2"/>
       <c r="I81" s="2"/>
       <c r="J81" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K81" s="3"/>
     </row>
     <row r="82" ht="28" spans="1:11">
       <c r="A82" s="17" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B82" s="14">
         <v>3</v>
@@ -4927,16 +4967,16 @@
         <v>13</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I82" s="2"/>
       <c r="J82" s="3"/>
@@ -4959,8 +4999,157 @@
       <c r="J83" s="3"/>
       <c r="K83" s="3"/>
     </row>
+    <row r="84" ht="42" spans="1:11">
+      <c r="A84" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="B84" s="25">
+        <v>0</v>
+      </c>
+      <c r="C84" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="D84" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="E84" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="F84" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H84" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="I84" s="4"/>
+      <c r="J84" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="K84" s="5"/>
+    </row>
+    <row r="85" ht="42" spans="1:11">
+      <c r="A85" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="B85" s="25">
+        <v>2</v>
+      </c>
+      <c r="C85" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="D85" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F85" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H85" s="4"/>
+      <c r="I85" s="4"/>
+      <c r="J85" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="K85" s="5"/>
+    </row>
+    <row r="86" ht="28" spans="1:11">
+      <c r="A86" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="B86" s="25">
+        <v>0</v>
+      </c>
+      <c r="C86" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="D86" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="F86" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H86" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="I86" s="4"/>
+      <c r="J86" s="5"/>
+      <c r="K86" s="5"/>
+    </row>
+    <row r="87" spans="1:11">
+      <c r="A87" s="25"/>
+      <c r="B87" s="25"/>
+      <c r="C87" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="D87" s="25"/>
+      <c r="E87" s="5"/>
+      <c r="F87" s="5"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="4"/>
+      <c r="I87" s="4"/>
+      <c r="J87" s="5"/>
+      <c r="K87" s="5"/>
+    </row>
+    <row r="88" spans="1:11">
+      <c r="A88" s="25"/>
+      <c r="B88" s="25"/>
+      <c r="C88" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="D88" s="25"/>
+      <c r="E88" s="5"/>
+      <c r="F88" s="5"/>
+      <c r="G88" s="2"/>
+      <c r="H88" s="4"/>
+      <c r="I88" s="4"/>
+      <c r="J88" s="5"/>
+      <c r="K88" s="5"/>
+    </row>
+    <row r="89" spans="1:11">
+      <c r="A89" s="25"/>
+      <c r="B89" s="25"/>
+      <c r="C89" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="D89" s="25"/>
+      <c r="E89" s="5"/>
+      <c r="F89" s="5"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="4"/>
+      <c r="I89" s="4"/>
+      <c r="J89" s="5"/>
+      <c r="K89" s="5"/>
+    </row>
+    <row r="90" spans="1:11">
+      <c r="A90" s="25"/>
+      <c r="B90" s="25"/>
+      <c r="C90" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="D90" s="25"/>
+      <c r="E90" s="5"/>
+      <c r="F90" s="5"/>
+      <c r="G90" s="2"/>
+      <c r="H90" s="4"/>
+      <c r="I90" s="4"/>
+      <c r="J90" s="5"/>
+      <c r="K90" s="5"/>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K83" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K90" etc:filterBottomFollowUsedRange="0">
     <extLst>
       <etc:autoFilterAnalysis etc:version="v1" etc:showPane="0">
         <etc:analysisCharts>
@@ -5030,13 +5219,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C84 C85:C90 C91:C1048576">
       <formula1>"初始Basic,普通Common,罕见UnCommon,稀有Rare,先古Ancient,临时生成Token"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
       <formula1>"攻击,技能,能力"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G85">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G85 G86:G90">
       <formula1>"自身,单个敌人,单个队友,所有敌人,所有队友,随机敌人"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5062,16 +5251,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>10</v>
@@ -5082,13 +5271,13 @@
         <v>26</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="3"/>
@@ -5098,13 +5287,13 @@
         <v>35</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="3"/>
@@ -5114,17 +5303,17 @@
         <v>83</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="3" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" ht="56" spans="1:6">
@@ -5132,17 +5321,17 @@
         <v>82</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="3" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6" ht="28" spans="1:6">
@@ -5150,17 +5339,17 @@
         <v>95</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="3" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
     </row>
     <row r="7" ht="42" spans="1:6">
@@ -5168,17 +5357,17 @@
         <v>54</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8" ht="28" spans="1:6">
@@ -5186,17 +5375,17 @@
         <v>75</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -5204,13 +5393,13 @@
         <v>72</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>301</v>
-      </c>
       <c r="D9" s="2" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="3"/>
@@ -5220,13 +5409,13 @@
         <v>99</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>316</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>302</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="3"/>
@@ -5236,37 +5425,37 @@
         <v>96</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
     </row>
     <row r="12" ht="56" spans="1:6">
       <c r="A12" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="3" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -5274,311 +5463,311 @@
         <v>106</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="3"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="3"/>
     </row>
     <row r="15" ht="28" spans="1:6">
       <c r="A15" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="3" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
     </row>
     <row r="16" ht="28" spans="1:6">
       <c r="A16" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="F17" s="3"/>
     </row>
     <row r="18" ht="28" spans="1:6">
       <c r="A18" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="3"/>
     </row>
     <row r="19" ht="28" spans="1:6">
       <c r="A19" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="F19" s="3"/>
     </row>
     <row r="20" ht="28" spans="1:6">
       <c r="A20" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="3" t="s">
-        <v>332</v>
+        <v>346</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2" t="s">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="3"/>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="3"/>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="3"/>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
     </row>
     <row r="25" ht="28" spans="1:6">
       <c r="A25" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="3"/>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="3"/>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="3" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
     </row>
     <row r="28" ht="70" spans="1:6">
       <c r="A28" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
     </row>
     <row r="29" ht="42" spans="1:6">
       <c r="A29" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="5"/>
@@ -5605,10 +5794,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="C1" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -5632,32 +5821,32 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>354</v>
+        <v>368</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5691,7 +5880,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -5699,15 +5888,15 @@
         <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>355</v>
+        <v>369</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B3" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
     </row>
     <row r="4" ht="112" spans="1:2">
@@ -5715,7 +5904,7 @@
         <v>82</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -5723,7 +5912,7 @@
         <v>91</v>
       </c>
       <c r="B5" t="s">
-        <v>358</v>
+        <v>372</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -5731,7 +5920,7 @@
         <v>109</v>
       </c>
       <c r="B6" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -5752,31 +5941,31 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>360</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2" ht="28" spans="1:2">
       <c r="A2" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>362</v>
+        <v>376</v>
       </c>
     </row>
     <row r="3" ht="28" spans="1:2">
       <c r="A3" t="s">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>

--- a/docs/设计文档.xlsx
+++ b/docs/设计文档.xlsx
@@ -16,6 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">卡牌!$A$1:$K$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">能力!$A$1:$F$31</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="388">
   <si>
     <t>名称</t>
   </si>
@@ -600,6 +601,9 @@
   <si>
     <t>获得1层量子叠加
 下回合获得2点能量</t>
+  </si>
+  <si>
+    <t>量子叠加层数+1，能量+1</t>
   </si>
   <si>
     <t>量子叠加，能量</t>
@@ -1102,6 +1106,17 @@
     <t>基础伤害+10</t>
   </si>
   <si>
+    <t>幻影之镰</t>
+  </si>
+  <si>
+    <t>造成3点伤害
+获得3点格挡
+叠加：伤害和格挡值额外+2</t>
+  </si>
+  <si>
+    <t>基础伤害和格挡+1，叠加伤害和格挡+1</t>
+  </si>
+  <si>
     <t>永恒=一瞬</t>
   </si>
   <si>
@@ -1122,11 +1137,11 @@
     <t>罪罚两断之刃</t>
   </si>
   <si>
-    <t>造成14点伤害
-目标持有量子坍缩状态时，获得1点能量和1层量子叠加</t>
-  </si>
-  <si>
-    <t>基础伤害+6</t>
+    <t>造成12点伤害
+目标持有量子坍缩状态时，获得2点能量和1层量子叠加</t>
+  </si>
+  <si>
+    <t>基础伤害+4</t>
   </si>
   <si>
     <t>量子坍缩，能量，量子叠加</t>
@@ -1135,8 +1150,9 @@
     <t>X-10实验</t>
   </si>
   <si>
-    <t>打出抽牌堆的2张牌
-回合开始时，少抽1张牌</t>
+    <t>获得2层量子叠加
+打出抽牌堆的2张牌
+回合开始时，失去一层量子叠加，否则少抽1张牌</t>
   </si>
   <si>
     <t>打出牌数+1</t>
@@ -1161,6 +1177,9 @@
   </si>
   <si>
     <t>buff</t>
+  </si>
+  <si>
+    <t>否</t>
   </si>
   <si>
     <t>受到的伤害增加25%，造成的伤害减少25%，回合结束时减少1层</t>
@@ -1311,6 +1330,12 @@
   </si>
   <si>
     <t>触发叠加效果时，抽X张牌</t>
+  </si>
+  <si>
+    <t>回合开始时，失去X层量子叠加，否则少抽X张牌</t>
+  </si>
+  <si>
+    <t>量子叠加层数不足时，改为少抽牌</t>
   </si>
   <si>
     <t>类型/稀有度</t>
@@ -3896,7 +3921,7 @@
         <v>175</v>
       </c>
       <c r="F46" s="15" t="s">
-        <v>46</v>
+        <v>176</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>22</v>
@@ -3904,13 +3929,13 @@
       <c r="H46" s="16"/>
       <c r="I46" s="2"/>
       <c r="J46" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K46" s="3"/>
     </row>
     <row r="47" ht="42" spans="1:11">
       <c r="A47" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B47" s="14">
         <v>1</v>
@@ -3922,7 +3947,7 @@
         <v>19</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F47" s="15" t="s">
         <v>163</v>
@@ -3934,24 +3959,24 @@
       <c r="I47" s="2"/>
       <c r="J47" s="3"/>
       <c r="K47" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="48" spans="1:11">
       <c r="A48" s="21" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B48" s="14">
         <v>0</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D48" s="14" t="s">
         <v>19</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F48" s="15" t="s">
         <v>113</v>
@@ -3967,12 +3992,12 @@
         <v>35</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="21" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B49" s="14">
         <v>1</v>
@@ -3984,10 +4009,10 @@
         <v>19</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F49" s="15" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>22</v>
@@ -3998,12 +4023,12 @@
         <v>124</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="50" ht="28" spans="1:11">
       <c r="A50" s="21" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B50" s="14">
         <v>1</v>
@@ -4015,7 +4040,7 @@
         <v>19</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F50" s="15" t="s">
         <v>34</v>
@@ -4034,7 +4059,7 @@
     </row>
     <row r="51" ht="42" spans="1:11">
       <c r="A51" s="21" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B51" s="14">
         <v>1</v>
@@ -4046,10 +4071,10 @@
         <v>19</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F51" s="15" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>22</v>
@@ -4058,12 +4083,12 @@
       <c r="I51" s="2"/>
       <c r="J51" s="3"/>
       <c r="K51" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="52" ht="28" spans="1:11">
       <c r="A52" s="21" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B52" s="14">
         <v>1</v>
@@ -4075,7 +4100,7 @@
         <v>55</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F52" s="15" t="s">
         <v>74</v>
@@ -4090,7 +4115,7 @@
     </row>
     <row r="53" ht="28" spans="1:11">
       <c r="A53" s="21" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B53" s="14">
         <v>1</v>
@@ -4102,10 +4127,10 @@
         <v>19</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F53" s="15" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>22</v>
@@ -4113,13 +4138,13 @@
       <c r="H53" s="16"/>
       <c r="I53" s="2"/>
       <c r="J53" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K53" s="3"/>
     </row>
     <row r="54" ht="28" spans="1:11">
       <c r="A54" s="19" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B54" s="14">
         <v>0</v>
@@ -4131,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F54" s="15" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>22</v>
@@ -4150,7 +4175,7 @@
     </row>
     <row r="55" ht="28" spans="1:11">
       <c r="A55" s="21" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B55" s="14">
         <v>0</v>
@@ -4162,7 +4187,7 @@
         <v>19</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F55" s="15" t="s">
         <v>172</v>
@@ -4171,19 +4196,19 @@
         <v>22</v>
       </c>
       <c r="H55" s="16" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I55" s="2"/>
       <c r="J55" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="56" ht="42" spans="1:11">
       <c r="A56" s="21" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B56" s="14">
         <v>1</v>
@@ -4195,10 +4220,10 @@
         <v>13</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F56" s="15" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>131</v>
@@ -4210,7 +4235,7 @@
     </row>
     <row r="57" ht="42" spans="1:11">
       <c r="A57" s="17" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B57" s="14">
         <v>1</v>
@@ -4222,10 +4247,10 @@
         <v>13</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F57" s="15" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>61</v>
@@ -4236,15 +4261,15 @@
         <v>35</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="58" ht="28" spans="1:11">
       <c r="A58" s="20" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B58" s="14" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C58" s="14" t="s">
         <v>51</v>
@@ -4253,10 +4278,10 @@
         <v>19</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F58" s="15" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>61</v>
@@ -4264,13 +4289,13 @@
       <c r="H58" s="16"/>
       <c r="I58" s="2"/>
       <c r="J58" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K58" s="3"/>
     </row>
     <row r="59" ht="56" spans="1:11">
       <c r="A59" s="19" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B59" s="14">
         <v>0</v>
@@ -4282,10 +4307,10 @@
         <v>13</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F59" s="15" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>61</v>
@@ -4295,13 +4320,13 @@
       </c>
       <c r="I59" s="2"/>
       <c r="J59" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K59" s="3"/>
     </row>
     <row r="60" ht="70" spans="1:11">
       <c r="A60" s="21" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B60" s="14">
         <v>0</v>
@@ -4313,7 +4338,7 @@
         <v>55</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F60" s="15" t="s">
         <v>57</v>
@@ -4324,13 +4349,13 @@
       <c r="H60" s="16"/>
       <c r="I60" s="2"/>
       <c r="J60" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K60" s="3"/>
     </row>
     <row r="61" ht="42" spans="1:11">
       <c r="A61" s="17" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B61" s="14">
         <v>1</v>
@@ -4342,10 +4367,10 @@
         <v>13</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F61" s="15" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>16</v>
@@ -4355,13 +4380,13 @@
       </c>
       <c r="I61" s="2"/>
       <c r="J61" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K61" s="3"/>
     </row>
     <row r="62" ht="28" spans="1:11">
       <c r="A62" s="20" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B62" s="14">
         <v>0</v>
@@ -4373,10 +4398,10 @@
         <v>19</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F62" s="15" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>22</v>
@@ -4390,7 +4415,7 @@
     </row>
     <row r="63" ht="42" spans="1:11">
       <c r="A63" s="19" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B63" s="14">
         <v>0</v>
@@ -4402,10 +4427,10 @@
         <v>19</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F63" s="15" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>22</v>
@@ -4415,13 +4440,13 @@
       </c>
       <c r="I63" s="2"/>
       <c r="J63" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K63" s="3"/>
     </row>
     <row r="64" ht="28" spans="1:11">
       <c r="A64" s="19" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B64" s="14">
         <v>0</v>
@@ -4433,10 +4458,10 @@
         <v>13</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F64" s="15" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>22</v>
@@ -4450,7 +4475,7 @@
     </row>
     <row r="65" ht="28" spans="1:11">
       <c r="A65" s="22" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B65" s="14">
         <v>0</v>
@@ -4462,10 +4487,10 @@
         <v>19</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F65" s="15" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>16</v>
@@ -4476,12 +4501,12 @@
         <v>35</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="66" ht="42" spans="1:11">
       <c r="A66" s="22" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B66" s="14">
         <v>1</v>
@@ -4493,28 +4518,28 @@
         <v>19</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F66" s="15" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H66" s="16" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I66" s="2"/>
       <c r="J66" s="3" t="s">
         <v>95</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="67" ht="56" spans="1:11">
       <c r="A67" s="22" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B67" s="14">
         <v>1</v>
@@ -4526,13 +4551,13 @@
         <v>19</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F67" s="15" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H67" s="16"/>
       <c r="I67" s="2"/>
@@ -4540,15 +4565,15 @@
         <v>138</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="68" ht="28" spans="1:11">
       <c r="A68" s="19" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B68" s="14" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C68" s="14" t="s">
         <v>51</v>
@@ -4557,10 +4582,10 @@
         <v>13</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F68" s="15" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>131</v>
@@ -4572,7 +4597,7 @@
     </row>
     <row r="69" ht="28" spans="1:11">
       <c r="A69" s="17" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B69" s="14">
         <v>1</v>
@@ -4584,7 +4609,7 @@
         <v>13</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F69" s="15" t="s">
         <v>15</v>
@@ -4601,7 +4626,7 @@
     </row>
     <row r="70" ht="42" spans="1:11">
       <c r="A70" s="19" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B70" s="14">
         <v>3</v>
@@ -4613,10 +4638,10 @@
         <v>13</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F70" s="15" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>16</v>
@@ -4627,12 +4652,12 @@
       <c r="I70" s="2"/>
       <c r="J70" s="3"/>
       <c r="K70" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="71" ht="42" spans="1:11">
       <c r="A71" s="20" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B71" s="14">
         <v>1</v>
@@ -4644,10 +4669,10 @@
         <v>55</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F71" s="15" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>22</v>
@@ -4658,12 +4683,12 @@
         <v>124</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="72" ht="43.5" spans="1:11">
       <c r="A72" s="19" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B72" s="14">
         <v>1</v>
@@ -4675,10 +4700,10 @@
         <v>55</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>22</v>
@@ -4691,12 +4716,12 @@
         <v>91</v>
       </c>
       <c r="K72" s="23" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="73" ht="43.5" spans="1:11">
       <c r="A73" s="21" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B73" s="14">
         <v>1</v>
@@ -4708,10 +4733,10 @@
         <v>19</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>22</v>
@@ -4722,12 +4747,12 @@
       <c r="I73" s="2"/>
       <c r="J73" s="3"/>
       <c r="K73" s="24" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="74" ht="58" spans="1:11">
       <c r="A74" s="19" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B74" s="14">
         <v>1</v>
@@ -4739,10 +4764,10 @@
         <v>19</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>22</v>
@@ -4750,15 +4775,15 @@
       <c r="H74" s="2"/>
       <c r="I74" s="2"/>
       <c r="J74" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K74" s="23" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="75" ht="42" spans="1:11">
       <c r="A75" s="21" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B75" s="14">
         <v>1</v>
@@ -4770,7 +4795,7 @@
         <v>19</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>34</v>
@@ -4784,12 +4809,12 @@
       <c r="I75" s="2"/>
       <c r="J75" s="3"/>
       <c r="K75" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="76" ht="28" spans="1:11">
       <c r="A76" s="20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B76" s="14">
         <v>1</v>
@@ -4801,10 +4826,10 @@
         <v>13</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>16</v>
@@ -4820,7 +4845,7 @@
     </row>
     <row r="77" ht="28" spans="1:11">
       <c r="A77" s="19" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B77" s="14">
         <v>1</v>
@@ -4832,7 +4857,7 @@
         <v>55</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>34</v>
@@ -4845,13 +4870,13 @@
       </c>
       <c r="I77" s="2"/>
       <c r="J77" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K77" s="3"/>
     </row>
     <row r="78" spans="1:11">
       <c r="A78" s="17" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B78" s="14">
         <v>1</v>
@@ -4863,7 +4888,7 @@
         <v>55</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>34</v>
@@ -4880,7 +4905,7 @@
     </row>
     <row r="79" spans="1:11">
       <c r="A79" s="17" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B79" s="14">
         <v>2</v>
@@ -4892,7 +4917,7 @@
         <v>55</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>34</v>
@@ -4926,7 +4951,7 @@
     </row>
     <row r="81" ht="42" spans="1:11">
       <c r="A81" s="20" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B81" s="14">
         <v>1</v>
@@ -4938,10 +4963,10 @@
         <v>13</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>131</v>
@@ -4955,7 +4980,7 @@
     </row>
     <row r="82" ht="28" spans="1:11">
       <c r="A82" s="17" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B82" s="14">
         <v>3</v>
@@ -4967,41 +4992,53 @@
         <v>13</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I82" s="2"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
     </row>
-    <row r="83" spans="1:11">
-      <c r="A83" s="14"/>
-      <c r="B83" s="14"/>
+    <row r="83" ht="42" spans="1:11">
+      <c r="A83" s="17" t="s">
+        <v>299</v>
+      </c>
+      <c r="B83" s="14">
+        <v>0</v>
+      </c>
       <c r="C83" s="14" t="s">
         <v>51</v>
       </c>
       <c r="D83" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E83" s="3"/>
-      <c r="F83" s="3"/>
-      <c r="G83" s="2"/>
-      <c r="H83" s="2"/>
+      <c r="E83" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="I83" s="2"/>
       <c r="J83" s="3"/>
       <c r="K83" s="3"/>
     </row>
     <row r="84" ht="42" spans="1:11">
       <c r="A84" s="17" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B84" s="25">
         <v>0</v>
@@ -5013,26 +5050,26 @@
         <v>13</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="I84" s="4"/>
       <c r="J84" s="5" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="K84" s="5"/>
     </row>
     <row r="85" ht="42" spans="1:11">
       <c r="A85" s="17" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B85" s="25">
         <v>2</v>
@@ -5044,10 +5081,10 @@
         <v>13</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>16</v>
@@ -5055,13 +5092,13 @@
       <c r="H85" s="4"/>
       <c r="I85" s="4"/>
       <c r="J85" s="5" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K85" s="5"/>
     </row>
-    <row r="86" ht="28" spans="1:11">
+    <row r="86" ht="56" spans="1:11">
       <c r="A86" s="21" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B86" s="25">
         <v>0</v>
@@ -5073,19 +5110,21 @@
         <v>55</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="I86" s="4"/>
-      <c r="J86" s="5"/>
+      <c r="J86" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="K86" s="5"/>
     </row>
     <row r="87" spans="1:11">
@@ -5094,7 +5133,9 @@
       <c r="C87" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="D87" s="25"/>
+      <c r="D87" s="25" t="s">
+        <v>55</v>
+      </c>
       <c r="E87" s="5"/>
       <c r="F87" s="5"/>
       <c r="G87" s="2"/>
@@ -5109,7 +5150,9 @@
       <c r="C88" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="D88" s="25"/>
+      <c r="D88" s="25" t="s">
+        <v>55</v>
+      </c>
       <c r="E88" s="5"/>
       <c r="F88" s="5"/>
       <c r="G88" s="2"/>
@@ -5124,7 +5167,9 @@
       <c r="C89" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="D89" s="25"/>
+      <c r="D89" s="25" t="s">
+        <v>13</v>
+      </c>
       <c r="E89" s="5"/>
       <c r="F89" s="5"/>
       <c r="G89" s="2"/>
@@ -5139,7 +5184,9 @@
       <c r="C90" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="D90" s="25"/>
+      <c r="D90" s="25" t="s">
+        <v>19</v>
+      </c>
       <c r="E90" s="5"/>
       <c r="F90" s="5"/>
       <c r="G90" s="2"/>
@@ -5238,7 +5285,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="16.0909090909091" customWidth="1"/>
@@ -5251,16 +5298,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>10</v>
@@ -5271,15 +5318,17 @@
         <v>26</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="E2" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>321</v>
+      </c>
       <c r="F2" s="3"/>
     </row>
     <row r="3" spans="1:6">
@@ -5287,15 +5336,17 @@
         <v>35</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="E3" s="2"/>
+        <v>323</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>321</v>
+      </c>
       <c r="F3" s="3"/>
     </row>
     <row r="4" ht="42" spans="1:6">
@@ -5303,17 +5354,19 @@
         <v>83</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>315</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="E4" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>321</v>
+      </c>
       <c r="F4" s="3" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
     <row r="5" ht="56" spans="1:6">
@@ -5321,17 +5374,19 @@
         <v>82</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="E5" s="2"/>
       <c r="F5" s="3" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
     </row>
     <row r="6" ht="28" spans="1:6">
@@ -5339,17 +5394,19 @@
         <v>95</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="E6" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>321</v>
+      </c>
       <c r="F6" s="3" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="7" ht="42" spans="1:6">
@@ -5357,17 +5414,19 @@
         <v>54</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="E7" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>321</v>
+      </c>
       <c r="F7" s="3" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="8" ht="28" spans="1:6">
@@ -5375,17 +5434,19 @@
         <v>75</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="E8" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>321</v>
+      </c>
       <c r="F8" s="3" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -5393,15 +5454,17 @@
         <v>72</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="E9" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>321</v>
+      </c>
       <c r="F9" s="3"/>
     </row>
     <row r="10" ht="28" spans="1:6">
@@ -5409,15 +5472,17 @@
         <v>99</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="E10" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>321</v>
+      </c>
       <c r="F10" s="3"/>
     </row>
     <row r="11" ht="56" spans="1:6">
@@ -5425,19 +5490,19 @@
         <v>96</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="12" ht="56" spans="1:6">
@@ -5445,17 +5510,19 @@
         <v>124</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="E12" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>321</v>
+      </c>
       <c r="F12" s="3" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -5463,15 +5530,17 @@
         <v>106</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="E13" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>321</v>
+      </c>
       <c r="F13" s="3"/>
     </row>
     <row r="14" spans="1:6">
@@ -5479,15 +5548,17 @@
         <v>116</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="E14" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>321</v>
+      </c>
       <c r="F14" s="3"/>
     </row>
     <row r="15" ht="28" spans="1:6">
@@ -5495,17 +5566,19 @@
         <v>136</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="E15" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>321</v>
+      </c>
       <c r="F15" s="3" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="16" ht="28" spans="1:6">
@@ -5513,19 +5586,19 @@
         <v>152</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5533,16 +5606,16 @@
         <v>170</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="F17" s="3"/>
     </row>
@@ -5551,32 +5624,34 @@
         <v>158</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="E18" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>321</v>
+      </c>
       <c r="F18" s="3"/>
     </row>
     <row r="19" ht="28" spans="1:6">
       <c r="A19" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="F19" s="3"/>
     </row>
@@ -5585,194 +5660,233 @@
         <v>132</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="E20" s="2"/>
+        <v>323</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>321</v>
+      </c>
       <c r="F20" s="3" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="E21" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>321</v>
+      </c>
       <c r="F21" s="3"/>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="E22" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>321</v>
+      </c>
       <c r="F22" s="3"/>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="E23" s="2"/>
+        <v>323</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>321</v>
+      </c>
       <c r="F23" s="3"/>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="25" ht="28" spans="1:6">
       <c r="A25" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="E25" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>321</v>
+      </c>
       <c r="F25" s="3"/>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="E26" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>321</v>
+      </c>
       <c r="F26" s="3"/>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="E27" s="2"/>
+        <v>323</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>321</v>
+      </c>
       <c r="F27" s="3" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="28" ht="70" spans="1:6">
       <c r="A28" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="29" ht="42" spans="1:6">
       <c r="A29" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="E30" s="4"/>
+        <v>320</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>321</v>
+      </c>
       <c r="F30" s="5"/>
     </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>369</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F31" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -5794,10 +5908,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C1" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -5821,32 +5935,32 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5880,7 +5994,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -5888,15 +6002,15 @@
         <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B3" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
     </row>
     <row r="4" ht="112" spans="1:2">
@@ -5904,7 +6018,7 @@
         <v>82</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -5912,7 +6026,7 @@
         <v>91</v>
       </c>
       <c r="B5" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -5920,7 +6034,7 @@
         <v>109</v>
       </c>
       <c r="B6" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -5941,31 +6055,31 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
     </row>
     <row r="2" ht="28" spans="1:2">
       <c r="A2" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
     </row>
     <row r="3" ht="28" spans="1:2">
       <c r="A3" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>

--- a/docs/设计文档.xlsx
+++ b/docs/设计文档.xlsx
@@ -15,7 +15,7 @@
     <sheet name="草稿" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">卡牌!$A$1:$K$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">卡牌!$A$1:$K$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">能力!$A$1:$F$31</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="399">
   <si>
     <t>名称</t>
   </si>
@@ -668,7 +668,7 @@
     <t>白花郁血</t>
   </si>
   <si>
-    <t>在你的回合内，每失去一次生命值，获得2点格挡</t>
+    <t>在你的回合内，每失去一次生命值，获得3点格挡</t>
   </si>
   <si>
     <t>落英旋舞</t>
@@ -751,11 +751,11 @@
   </si>
   <si>
     <t>处于星环爆发状态下才可以打出
-对所有敌人造成14点伤害
+对所有敌人造成20点伤害
 结束星环爆发状态，结束前每剩余一层简并动能，获得10层星环能级</t>
   </si>
   <si>
-    <t>伤害+6</t>
+    <t>伤害+8</t>
   </si>
   <si>
     <t>简并动能，星环能级</t>
@@ -1052,6 +1052,9 @@
 目标死亡时，对所有其它敌人造成相当于其最大生命值的伤害。</t>
   </si>
   <si>
+    <t>耗能减少1，量子坍缩层数+1</t>
+  </si>
+  <si>
     <t>注意能力需要可以叠加，叠加可造成多倍最大生命值伤害</t>
   </si>
   <si>
@@ -1084,6 +1087,12 @@
   </si>
   <si>
     <t>触发叠加效果时，抽1张牌</t>
+  </si>
+  <si>
+    <t>存在泡影</t>
+  </si>
+  <si>
+    <t>触发叠加效果时，对随机敌人造成5点伤害</t>
   </si>
   <si>
     <t>如细雨，静润不辍</t>
@@ -1161,6 +1170,24 @@
     <t>固有</t>
   </si>
   <si>
+    <t>盛开，不惧凋零</t>
+  </si>
+  <si>
+    <t>回合开始时，获得X层愈合，若X的值不小于2则多抽1张牌，若X的值不小于4，则多抽2张牌</t>
+  </si>
+  <si>
+    <t>抽牌数在叠加能力时获取对应power的对象并增加其动态变量的值以实现叠加。</t>
+  </si>
+  <si>
+    <t>如惊霆，锻韧于心</t>
+  </si>
+  <si>
+    <t>使你的愈合层数翻倍</t>
+  </si>
+  <si>
+    <t>移除消耗</t>
+  </si>
+  <si>
     <t>说明</t>
   </si>
   <si>
@@ -1336,6 +1363,12 @@
   </si>
   <si>
     <t>量子叠加层数不足时，改为少抽牌</t>
+  </si>
+  <si>
+    <t>回合开始时，获得X层愈合，抽Y张牌</t>
+  </si>
+  <si>
+    <t>层数表示愈合获得数量，抽牌数由Cards动态变量保存，并由卡牌打出时进行更新</t>
   </si>
   <si>
     <t>类型/稀有度</t>
@@ -2525,7 +2558,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K90"/>
+  <dimension ref="A1:K88"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="19.0909090909091" style="7" customWidth="1"/>
@@ -4087,7 +4120,7 @@
       </c>
     </row>
     <row r="52" ht="28" spans="1:11">
-      <c r="A52" s="21" t="s">
+      <c r="A52" s="20" t="s">
         <v>195</v>
       </c>
       <c r="B52" s="14">
@@ -4798,7 +4831,7 @@
         <v>281</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>34</v>
+        <v>282</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>16</v>
@@ -4809,12 +4842,12 @@
       <c r="I75" s="2"/>
       <c r="J75" s="3"/>
       <c r="K75" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="76" ht="28" spans="1:11">
       <c r="A76" s="20" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B76" s="14">
         <v>1</v>
@@ -4826,10 +4859,10 @@
         <v>13</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>16</v>
@@ -4845,7 +4878,7 @@
     </row>
     <row r="77" ht="28" spans="1:11">
       <c r="A77" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B77" s="14">
         <v>1</v>
@@ -4857,7 +4890,7 @@
         <v>55</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>34</v>
@@ -4870,13 +4903,13 @@
       </c>
       <c r="I77" s="2"/>
       <c r="J77" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K77" s="3"/>
     </row>
     <row r="78" spans="1:11">
       <c r="A78" s="17" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B78" s="14">
         <v>1</v>
@@ -4888,7 +4921,7 @@
         <v>55</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>34</v>
@@ -4905,7 +4938,7 @@
     </row>
     <row r="79" spans="1:11">
       <c r="A79" s="17" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B79" s="14">
         <v>2</v>
@@ -4917,7 +4950,7 @@
         <v>55</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>34</v>
@@ -4933,25 +4966,37 @@
       <c r="K79" s="3"/>
     </row>
     <row r="80" spans="1:11">
-      <c r="A80" s="14"/>
-      <c r="B80" s="14"/>
+      <c r="A80" s="17" t="s">
+        <v>294</v>
+      </c>
+      <c r="B80" s="14">
+        <v>1</v>
+      </c>
       <c r="C80" s="14" t="s">
         <v>51</v>
       </c>
       <c r="D80" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="E80" s="3"/>
-      <c r="F80" s="3"/>
-      <c r="G80" s="2"/>
+      <c r="E80" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="H80" s="2"/>
       <c r="I80" s="2"/>
-      <c r="J80" s="3"/>
+      <c r="J80" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="K80" s="3"/>
     </row>
     <row r="81" ht="42" spans="1:11">
       <c r="A81" s="20" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B81" s="14">
         <v>1</v>
@@ -4963,10 +5008,10 @@
         <v>13</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>131</v>
@@ -4980,7 +5025,7 @@
     </row>
     <row r="82" ht="28" spans="1:11">
       <c r="A82" s="17" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B82" s="14">
         <v>3</v>
@@ -4992,10 +5037,10 @@
         <v>13</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>16</v>
@@ -5009,7 +5054,7 @@
     </row>
     <row r="83" ht="42" spans="1:11">
       <c r="A83" s="17" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B83" s="14">
         <v>0</v>
@@ -5021,10 +5066,10 @@
         <v>13</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>16</v>
@@ -5038,7 +5083,7 @@
     </row>
     <row r="84" ht="42" spans="1:11">
       <c r="A84" s="17" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B84" s="25">
         <v>0</v>
@@ -5050,26 +5095,26 @@
         <v>13</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="I84" s="4"/>
       <c r="J84" s="5" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="K84" s="5"/>
     </row>
     <row r="85" ht="42" spans="1:11">
       <c r="A85" s="17" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B85" s="25">
         <v>2</v>
@@ -5081,10 +5126,10 @@
         <v>13</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>16</v>
@@ -5092,13 +5137,13 @@
       <c r="H85" s="4"/>
       <c r="I85" s="4"/>
       <c r="J85" s="5" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="K85" s="5"/>
     </row>
     <row r="86" ht="56" spans="1:11">
       <c r="A86" s="21" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B86" s="25">
         <v>0</v>
@@ -5110,16 +5155,16 @@
         <v>55</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="I86" s="4"/>
       <c r="J86" s="5" t="s">
@@ -5127,76 +5172,70 @@
       </c>
       <c r="K86" s="5"/>
     </row>
-    <row r="87" spans="1:11">
-      <c r="A87" s="25"/>
-      <c r="B87" s="25"/>
+    <row r="87" ht="42" spans="1:11">
+      <c r="A87" s="20" t="s">
+        <v>318</v>
+      </c>
+      <c r="B87" s="25" t="s">
+        <v>217</v>
+      </c>
       <c r="C87" s="25" t="s">
         <v>69</v>
       </c>
       <c r="D87" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="E87" s="5"/>
-      <c r="F87" s="5"/>
-      <c r="G87" s="2"/>
+      <c r="E87" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="F87" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="H87" s="4"/>
       <c r="I87" s="4"/>
-      <c r="J87" s="5"/>
-      <c r="K87" s="5"/>
+      <c r="J87" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="K87" s="5" t="s">
+        <v>320</v>
+      </c>
     </row>
     <row r="88" spans="1:11">
-      <c r="A88" s="25"/>
-      <c r="B88" s="25"/>
+      <c r="A88" s="20" t="s">
+        <v>321</v>
+      </c>
+      <c r="B88" s="25">
+        <v>1</v>
+      </c>
       <c r="C88" s="25" t="s">
         <v>69</v>
       </c>
       <c r="D88" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="E88" s="5"/>
-      <c r="F88" s="5"/>
-      <c r="G88" s="2"/>
-      <c r="H88" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="F88" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H88" s="4" t="s">
+        <v>143</v>
+      </c>
       <c r="I88" s="4"/>
-      <c r="J88" s="5"/>
+      <c r="J88" s="5" t="s">
+        <v>124</v>
+      </c>
       <c r="K88" s="5"/>
     </row>
-    <row r="89" spans="1:11">
-      <c r="A89" s="25"/>
-      <c r="B89" s="25"/>
-      <c r="C89" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="D89" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="E89" s="5"/>
-      <c r="F89" s="5"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="4"/>
-      <c r="I89" s="4"/>
-      <c r="J89" s="5"/>
-      <c r="K89" s="5"/>
-    </row>
-    <row r="90" spans="1:11">
-      <c r="A90" s="25"/>
-      <c r="B90" s="25"/>
-      <c r="C90" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="D90" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="E90" s="5"/>
-      <c r="F90" s="5"/>
-      <c r="G90" s="2"/>
-      <c r="H90" s="4"/>
-      <c r="I90" s="4"/>
-      <c r="J90" s="5"/>
-      <c r="K90" s="5"/>
-    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K90" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K88" etc:filterBottomFollowUsedRange="0">
     <extLst>
       <etc:autoFilterAnalysis etc:version="v1" etc:showPane="0">
         <etc:analysisCharts>
@@ -5266,14 +5305,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C84 C85:C90 C91:C1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C88 C2:C84 C85:C87 C89:C1048576">
       <formula1>"初始Basic,普通Common,罕见UnCommon,稀有Rare,先古Ancient,临时生成Token"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G88 G2:G85 G86:G87">
+      <formula1>"自身,单个敌人,单个队友,所有敌人,所有队友,随机敌人"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D87 D88:D1048576">
       <formula1>"攻击,技能,能力"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G85 G86:G90">
-      <formula1>"自身,单个敌人,单个队友,所有敌人,所有队友,随机敌人"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5285,7 +5324,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="16.0909090909091" customWidth="1"/>
@@ -5298,16 +5337,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>10</v>
@@ -5318,16 +5357,16 @@
         <v>26</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="F2" s="3"/>
     </row>
@@ -5336,16 +5375,16 @@
         <v>35</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="F3" s="3"/>
     </row>
@@ -5354,19 +5393,19 @@
         <v>83</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
     </row>
     <row r="5" ht="56" spans="1:6">
@@ -5374,19 +5413,19 @@
         <v>82</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
     </row>
     <row r="6" ht="28" spans="1:6">
@@ -5394,19 +5433,19 @@
         <v>95</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>319</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
     </row>
     <row r="7" ht="42" spans="1:6">
@@ -5414,19 +5453,19 @@
         <v>54</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>321</v>
-      </c>
       <c r="F7" s="3" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" ht="28" spans="1:6">
@@ -5434,19 +5473,19 @@
         <v>75</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -5454,16 +5493,16 @@
         <v>72</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="F9" s="3"/>
     </row>
@@ -5472,16 +5511,16 @@
         <v>99</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="F10" s="3"/>
     </row>
@@ -5490,19 +5529,19 @@
         <v>96</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
     </row>
     <row r="12" ht="56" spans="1:6">
@@ -5510,19 +5549,19 @@
         <v>124</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -5530,16 +5569,16 @@
         <v>106</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="F13" s="3"/>
     </row>
@@ -5548,16 +5587,16 @@
         <v>116</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="F14" s="3"/>
     </row>
@@ -5566,19 +5605,19 @@
         <v>136</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
     </row>
     <row r="16" ht="28" spans="1:6">
@@ -5586,19 +5625,19 @@
         <v>152</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5606,16 +5645,16 @@
         <v>170</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="F17" s="3"/>
     </row>
@@ -5624,16 +5663,16 @@
         <v>158</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="F18" s="3"/>
     </row>
@@ -5642,16 +5681,16 @@
         <v>191</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="F19" s="3"/>
     </row>
@@ -5660,36 +5699,36 @@
         <v>132</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="F21" s="3"/>
     </row>
@@ -5698,16 +5737,16 @@
         <v>195</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="F22" s="3"/>
     </row>
@@ -5716,16 +5755,16 @@
         <v>225</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="F23" s="3"/>
     </row>
@@ -5734,19 +5773,19 @@
         <v>252</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
     </row>
     <row r="25" ht="28" spans="1:6">
@@ -5754,16 +5793,16 @@
         <v>267</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="F25" s="3"/>
     </row>
@@ -5772,16 +5811,16 @@
         <v>263</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="F26" s="3"/>
     </row>
@@ -5790,97 +5829,117 @@
         <v>280</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
     </row>
     <row r="28" ht="70" spans="1:6">
       <c r="A28" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
     </row>
     <row r="29" ht="42" spans="1:6">
       <c r="A29" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="F30" s="5"/>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="4" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>369</v>
+        <v>378</v>
+      </c>
+    </row>
+    <row r="32" ht="42" spans="1:6">
+      <c r="A32" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -5908,10 +5967,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="C1" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -5935,32 +5994,32 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5994,7 +6053,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -6002,7 +6061,7 @@
         <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -6010,7 +6069,7 @@
         <v>206</v>
       </c>
       <c r="B3" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
     </row>
     <row r="4" ht="112" spans="1:2">
@@ -6018,7 +6077,7 @@
         <v>82</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -6026,7 +6085,7 @@
         <v>91</v>
       </c>
       <c r="B5" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -6034,7 +6093,7 @@
         <v>109</v>
       </c>
       <c r="B6" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
     </row>
   </sheetData>
@@ -6055,31 +6114,31 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
     </row>
     <row r="2" ht="28" spans="1:2">
       <c r="A2" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
     </row>
     <row r="3" ht="28" spans="1:2">
       <c r="A3" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>

--- a/docs/设计文档.xlsx
+++ b/docs/设计文档.xlsx
@@ -15,7 +15,7 @@
     <sheet name="草稿" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">卡牌!$A$1:$K$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">卡牌!$A$1:$K$89</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">能力!$A$1:$F$31</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="402">
   <si>
     <t>名称</t>
   </si>
@@ -132,23 +132,25 @@
     <t>叠加</t>
   </si>
   <si>
-    <t>化虚为实</t>
-  </si>
-  <si>
-    <t>先古Ancient</t>
-  </si>
-  <si>
-    <t>造成12点伤害
-叠加：额外造成20点伤害并施加2层量子坍缩</t>
-  </si>
-  <si>
-    <t>耗能减少1</t>
+    <t>落英</t>
+  </si>
+  <si>
+    <t>临时生成Token</t>
+  </si>
+  <si>
+    <t>施加一层量子坍缩</t>
+  </si>
+  <si>
+    <t>获得保留</t>
+  </si>
+  <si>
+    <t>消耗</t>
   </si>
   <si>
     <t>量子坍缩</t>
   </si>
   <si>
-    <t>由坍缩攻击+欧洛巴斯之触变化</t>
+    <t>加入TokenCardPool</t>
   </si>
   <si>
     <t>纠缠护盾</t>
@@ -194,100 +196,6 @@
     <t>格挡值+4，量子叠加层数+1</t>
   </si>
   <si>
-    <t>实体坍缩</t>
-  </si>
-  <si>
-    <t>罕见UnCommon</t>
-  </si>
-  <si>
-    <t>造成10点伤害
-叠加：额外造成6点伤害并对目标施加2层量子坍缩</t>
-  </si>
-  <si>
-    <t>基础伤害+2，叠加额外伤害+2，施加的量子坍缩层数+1</t>
-  </si>
-  <si>
-    <t>量子不确定性</t>
-  </si>
-  <si>
-    <t>能力</t>
-  </si>
-  <si>
-    <t>持有量子叠加时，从卡牌中获得的格挡值额外增加3</t>
-  </si>
-  <si>
-    <t>获得固有</t>
-  </si>
-  <si>
-    <t>开启门扉</t>
-  </si>
-  <si>
-    <t>对所有敌人施加1层虚弱
-叠加：改为对所有敌人施加2层易伤和2层虚弱</t>
-  </si>
-  <si>
-    <t>叠加施加易伤和虚弱层数+1</t>
-  </si>
-  <si>
-    <t>所有敌人</t>
-  </si>
-  <si>
-    <t>虚弱、易伤</t>
-  </si>
-  <si>
-    <t>粒子波动</t>
-  </si>
-  <si>
-    <t>失去3点生命值
-获得1层量子叠加
-抽2张牌</t>
-  </si>
-  <si>
-    <t>蝶舞</t>
-  </si>
-  <si>
-    <t>造成4点伤害
-触发叠加效果时，将这张牌放入你的手牌</t>
-  </si>
-  <si>
-    <t>伤害增加2</t>
-  </si>
-  <si>
-    <t>静谧利刃</t>
-  </si>
-  <si>
-    <t>稀有Rare</t>
-  </si>
-  <si>
-    <t>对随机敌人造成4点伤害3次
-叠加：消耗所有量子叠加层数，每消耗1层对所有敌人造成8点伤害1次</t>
-  </si>
-  <si>
-    <t>叠加造成的群体伤害增加3</t>
-  </si>
-  <si>
-    <t>量子躯体</t>
-  </si>
-  <si>
-    <t>触发叠加效果时，获得4点格挡</t>
-  </si>
-  <si>
-    <t>格挡增加1</t>
-  </si>
-  <si>
-    <t>量子形态</t>
-  </si>
-  <si>
-    <t>回合开始时，获得2层量子叠加。
-每回合首次触发叠加效果时，抽2张牌。</t>
-  </si>
-  <si>
-    <t>量子叠加层数+1，抽牌数+1</t>
-  </si>
-  <si>
-    <t>触发叠加效果可以由SeleeHook实现</t>
-  </si>
-  <si>
     <t>星环吸积</t>
   </si>
   <si>
@@ -326,99 +234,10 @@
 共鸣：改为造成6点伤害3次</t>
   </si>
   <si>
+    <t>伤害增加2</t>
+  </si>
+  <si>
     <t>共鸣</t>
-  </si>
-  <si>
-    <t>羽落映花</t>
-  </si>
-  <si>
-    <t>对所有敌人造成4点伤害
-当前未处于星环爆发状态时，获得1层简并动能</t>
-  </si>
-  <si>
-    <t>伤害增加2，简并动能层数增加1</t>
-  </si>
-  <si>
-    <t>简并动能</t>
-  </si>
-  <si>
-    <t>灵羽沐心</t>
-  </si>
-  <si>
-    <t>你接下来每打出一张攻击牌，获得10层星环能级，可触发4次</t>
-  </si>
-  <si>
-    <t>星环能级增加5</t>
-  </si>
-  <si>
-    <t>星环盈余</t>
-  </si>
-  <si>
-    <t>进入星环爆发状态时，获得25层星环能级
-星环爆发状态下再次进入时不触发</t>
-  </si>
-  <si>
-    <t>获得星环能级增加10</t>
-  </si>
-  <si>
-    <t>春风化雨</t>
-  </si>
-  <si>
-    <t>获得8点格挡
-获得15层星环能级
-叠加：额外获得4点格挡和20层星环能级</t>
-  </si>
-  <si>
-    <t>基础格挡+2，叠加格挡+2，叠加星环能级+10</t>
-  </si>
-  <si>
-    <t>星环爆发，叠加</t>
-  </si>
-  <si>
-    <t>始终如一</t>
-  </si>
-  <si>
-    <t>共鸣攻击造成的伤害增加3</t>
-  </si>
-  <si>
-    <t>共鸣攻击伤害额外+1</t>
-  </si>
-  <si>
-    <t>共鸣攻击</t>
-  </si>
-  <si>
-    <t>监听共鸣攻击只需要在攻击牌打出前或计算伤害时判断是否持有简并动能状态</t>
-  </si>
-  <si>
-    <t>如晚星，谧引归途</t>
-  </si>
-  <si>
-    <t>进入星环爆发状态</t>
-  </si>
-  <si>
-    <t>获得保留</t>
-  </si>
-  <si>
-    <t>星环爆发，消耗</t>
-  </si>
-  <si>
-    <t>此方法进入星环爆发时保留星环能级</t>
-  </si>
-  <si>
-    <t>深海的幻梦</t>
-  </si>
-  <si>
-    <t>发动共鸣攻击时，对所有敌人造成8点伤害</t>
-  </si>
-  <si>
-    <t>伤害增加3</t>
-  </si>
-  <si>
-    <t>暗影洪流</t>
-  </si>
-  <si>
-    <t>对所有敌人造成10点伤害2次
-共鸣：获得2层简并动能</t>
   </si>
   <si>
     <t>绀海之灵</t>
@@ -456,104 +275,6 @@
     <t>随机敌人</t>
   </si>
   <si>
-    <t>抓捕鸭鸭</t>
-  </si>
-  <si>
-    <t>若目标的意图为攻击，自身获得5层愈合，使目标本回合失去4点力量</t>
-  </si>
-  <si>
-    <t>愈合层数+2，失去力量层数+2</t>
-  </si>
-  <si>
-    <t>愈合，力量</t>
-  </si>
-  <si>
-    <t>白花领域</t>
-  </si>
-  <si>
-    <t>回合开始时，失去1点生命值，获得1点能量</t>
-  </si>
-  <si>
-    <t>能量</t>
-  </si>
-  <si>
-    <t>base.EnergyHoverTip
-能量需描述为能量图标{Amount:energyIcons()}</t>
-  </si>
-  <si>
-    <t>度愈新生</t>
-  </si>
-  <si>
-    <t>获得9层愈合</t>
-  </si>
-  <si>
-    <t>愈合层数+3</t>
-  </si>
-  <si>
-    <t>消耗</t>
-  </si>
-  <si>
-    <t>万灵生息</t>
-  </si>
-  <si>
-    <t>对所有敌人造成相当于愈合层数3倍的伤害
-失去所有愈合层数</t>
-  </si>
-  <si>
-    <t>隧穿效应</t>
-  </si>
-  <si>
-    <t>失去3点生命值
-抽2张牌
-下回合抽1张牌</t>
-  </si>
-  <si>
-    <t>立即抽牌数+1</t>
-  </si>
-  <si>
-    <t>良好作息</t>
-  </si>
-  <si>
-    <t>回复相当于愈合层数50%的生命值</t>
-  </si>
-  <si>
-    <t>此牌不会消耗愈合层数</t>
-  </si>
-  <si>
-    <t>晓歌露影</t>
-  </si>
-  <si>
-    <t>目标本回合每受到一次攻击，你获得2层愈合</t>
-  </si>
-  <si>
-    <t>如朝露，消散于晨曦</t>
-  </si>
-  <si>
-    <t>失去6点生命值
-对所有敌人造成21点伤害
-如果此次攻击击杀了敌人，回复6点生命值并再次打出此牌</t>
-  </si>
-  <si>
-    <t>伤害增加7</t>
-  </si>
-  <si>
-    <t>自动打出牌：
-CardCmd.AutoPlay(choiceContext, card, target)
-可持续重复打出直到未能击杀敌人</t>
-  </si>
-  <si>
-    <t>仁术</t>
-  </si>
-  <si>
-    <t>回合开始时，消耗抽牌堆的一张牌，获得3层愈合。
-若消耗的牌为状态或诅咒牌，获得的愈合层数翻倍。</t>
-  </si>
-  <si>
-    <t>在抽牌前触发
-若抽牌堆为空，则不触发消耗效果
-消耗的牌由玩家选择</t>
-  </si>
-  <si>
     <t>点水惊涟</t>
   </si>
   <si>
@@ -584,93 +305,6 @@
     <t>星环能级+5，抽牌数+1</t>
   </si>
   <si>
-    <t>纷扬风翎的邀约</t>
-  </si>
-  <si>
-    <t>下次进入星环爆发状态时，获得2点能量并抽2张牌</t>
-  </si>
-  <si>
-    <t>获得能量+1</t>
-  </si>
-  <si>
-    <t>在星环爆发状态下再次进入星环爆发也生效</t>
-  </si>
-  <si>
-    <t>幻海少女</t>
-  </si>
-  <si>
-    <t>获得1层量子叠加
-下回合获得2点能量</t>
-  </si>
-  <si>
-    <t>量子叠加层数+1，能量+1</t>
-  </si>
-  <si>
-    <t>量子叠加，能量</t>
-  </si>
-  <si>
-    <t>夏花摇曳</t>
-  </si>
-  <si>
-    <t>抽1张牌
-选择一张手牌变化为落英
-叠加：可变化最多3张手牌</t>
-  </si>
-  <si>
-    <t>添加“消耗”和卡牌“落英”的ExtraHoverTip</t>
-  </si>
-  <si>
-    <t>落英</t>
-  </si>
-  <si>
-    <t>临时生成Token</t>
-  </si>
-  <si>
-    <t>施加一层量子坍缩</t>
-  </si>
-  <si>
-    <t>加入TokenCardPool</t>
-  </si>
-  <si>
-    <t>清泉涤愈</t>
-  </si>
-  <si>
-    <t>消耗一张手牌，获得3层愈合</t>
-  </si>
-  <si>
-    <t>愈合层数+2</t>
-  </si>
-  <si>
-    <t>添加“消耗”的ExtraHoverTip</t>
-  </si>
-  <si>
-    <t>如飞鸟，掠动风漪</t>
-  </si>
-  <si>
-    <t>获得50层星环能级
-抽3张牌</t>
-  </si>
-  <si>
-    <t>七拳碎海</t>
-  </si>
-  <si>
-    <t>接下来的7张攻击牌造成的伤害+2
-其中第7张攻击牌造成的伤害额外+10</t>
-  </si>
-  <si>
-    <t>最后一次攻击伤害+8</t>
-  </si>
-  <si>
-    <t>每打出一张攻击牌算一次攻击，而不是每造成一次伤害
-第7张攻击牌共计+13/21伤害</t>
-  </si>
-  <si>
-    <t>白花郁血</t>
-  </si>
-  <si>
-    <t>在你的回合内，每失去一次生命值，获得3点格挡</t>
-  </si>
-  <si>
     <t>落英旋舞</t>
   </si>
   <si>
@@ -691,87 +325,6 @@
   </si>
   <si>
     <t>格挡值+2，星环能级+5</t>
-  </si>
-  <si>
-    <t>光影相携</t>
-  </si>
-  <si>
-    <t>叠加2：获得2点能量，将一张落英加入抽牌堆</t>
-  </si>
-  <si>
-    <t>叠加X</t>
-  </si>
-  <si>
-    <t>能量，落英卡牌</t>
-  </si>
-  <si>
-    <t>生成的牌加入抽牌堆随机位置</t>
-  </si>
-  <si>
-    <t>天坠的星辉</t>
-  </si>
-  <si>
-    <t>对随机敌人造成7点伤害1次
-打出后本场战斗中这张牌的伤害和攻击次数增加1</t>
-  </si>
-  <si>
-    <t>基础攻击次数改为2次</t>
-  </si>
-  <si>
-    <t>诞生=终末</t>
-  </si>
-  <si>
-    <t>对所有敌人造成9点伤害
-使所有量子坍缩状态的敌人失去相当于10%的最大生命值的生命值</t>
-  </si>
-  <si>
-    <t>基础伤害+3，比例增加5%</t>
-  </si>
-  <si>
-    <t>失去生命值效果向下取整，至少为1</t>
-  </si>
-  <si>
-    <t>微光蒙心</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>获得3X层愈合
-对所有敌人施加X层虚弱</t>
-  </si>
-  <si>
-    <t>愈合层数改为4X，虚弱层数改为X+1</t>
-  </si>
-  <si>
-    <t>愈合，虚弱</t>
-  </si>
-  <si>
-    <t>溯洄海语的摇篮</t>
-  </si>
-  <si>
-    <t>处于星环爆发状态下才可以打出
-对所有敌人造成20点伤害
-结束星环爆发状态，结束前每剩余一层简并动能，获得10层星环能级</t>
-  </si>
-  <si>
-    <t>伤害+8</t>
-  </si>
-  <si>
-    <t>简并动能，星环能级</t>
-  </si>
-  <si>
-    <t>初醒新芽</t>
-  </si>
-  <si>
-    <t>获得3层量子叠加
-获得2点能量
-获得10层愈合
-获得30层星环能级
-每回合开始时，失去2点生命值</t>
-  </si>
-  <si>
-    <t>量子叠加，能量，星环能级，愈合</t>
   </si>
   <si>
     <t>明光=暗影</t>
@@ -798,85 +351,6 @@
     <t>格挡+1，愈合层数+2</t>
   </si>
   <si>
-    <t>诚勇</t>
-  </si>
-  <si>
-    <t>失去3点生命值
-获得20层星环能级
-获得1层简并动能</t>
-  </si>
-  <si>
-    <t>星环能级+10</t>
-  </si>
-  <si>
-    <t>星环能级，简并动能</t>
-  </si>
-  <si>
-    <t>甘霖回响</t>
-  </si>
-  <si>
-    <t>造成5点伤害
-共鸣：打出后返回手牌</t>
-  </si>
-  <si>
-    <t>伤害+2</t>
-  </si>
-  <si>
-    <t>爱v频道</t>
-  </si>
-  <si>
-    <t>移除目标的格挡。
-施加相当于玩家数量的量子坍缩。</t>
-  </si>
-  <si>
-    <t>添加保留</t>
-  </si>
-  <si>
-    <t>多人游戏限定</t>
-  </si>
-  <si>
-    <t>情报交易</t>
-  </si>
-  <si>
-    <t>使另一名玩家获得9点格挡。
-叠加：额外给予8点格挡。
-共鸣：目标玩家获得1层简并动能</t>
-  </si>
-  <si>
-    <t>基础格挡+3，叠加格挡+3</t>
-  </si>
-  <si>
-    <t>单个队友</t>
-  </si>
-  <si>
-    <t>叠加，共鸣，保留</t>
-  </si>
-  <si>
-    <t>多人游戏限定
-触发共鸣不消耗简并动能</t>
-  </si>
-  <si>
-    <t>身份互换</t>
-  </si>
-  <si>
-    <t>另一名玩家获得2点能量，抽2张牌
-目标本回合结束时，获得相当于目标格挡值50%的格挡。
-结束你的回合</t>
-  </si>
-  <si>
-    <t>给予能量+1，抽牌+1</t>
-  </si>
-  <si>
-    <t>绽放</t>
-  </si>
-  <si>
-    <t>对随机敌人造成9点伤害X次
-获得10X点星环能级</t>
-  </si>
-  <si>
-    <t>基础伤害+3，星环能级变为14X</t>
-  </si>
-  <si>
     <t>习练</t>
   </si>
   <si>
@@ -884,110 +358,7 @@
 叠加：耗能变为0</t>
   </si>
   <si>
-    <t>飞漾涤痕</t>
-  </si>
-  <si>
-    <t>造成6点伤害3次
-每发动一次共鸣攻击，这张牌在本场战斗中的耗能减少1</t>
-  </si>
-  <si>
-    <t>EnergyCost.AddThisCombat(-1);</t>
-  </si>
-  <si>
-    <t>凋零，只为盛开</t>
-  </si>
-  <si>
-    <t>失去6点生命值
-获得6层愈合
-战斗结束时，回复8点生命值</t>
-  </si>
-  <si>
-    <t>愈合层数+3，回复生命+4</t>
-  </si>
-  <si>
-    <t>战斗结束：
-AfterCombatEnd</t>
-  </si>
-  <si>
-    <t>连理星</t>
-  </si>
-  <si>
-    <t>发动共鸣攻击时，获得1点格挡
-若处于星环爆发状态下，额外获得2点格挡</t>
-  </si>
-  <si>
-    <t>基础格挡+1，爆发格挡+1</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>注意能力需要可以叠加</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>关键字</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t>HoverTips
-HoverTipFactory.FromKeyword(...)</t>
-    </r>
-  </si>
-  <si>
-    <t>抚羽归巢</t>
-  </si>
-  <si>
-    <t>将弃牌堆中最多2张牌加入抽牌堆，使其下次打出免费</t>
-  </si>
-  <si>
-    <t>可选牌数+1</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>下次免费打出：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-card.EnergyCost.SetUntilPlayed(0);
-card.SetStarCostUntilPlayed(0);</t>
-    </r>
+    <t>所有敌人</t>
   </si>
   <si>
     <t>静待翩飞</t>
@@ -1045,19 +416,6 @@
     </r>
   </si>
   <si>
-    <t>天秤崩落之刻</t>
-  </si>
-  <si>
-    <t>施加2层量子坍缩
-目标死亡时，对所有其它敌人造成相当于其最大生命值的伤害。</t>
-  </si>
-  <si>
-    <t>耗能减少1，量子坍缩层数+1</t>
-  </si>
-  <si>
-    <t>注意能力需要可以叠加，叠加可造成多倍最大生命值伤害</t>
-  </si>
-  <si>
     <t>愈合打击</t>
   </si>
   <si>
@@ -1068,10 +426,417 @@
     <t>伤害+4</t>
   </si>
   <si>
+    <t>实体坍缩</t>
+  </si>
+  <si>
+    <t>罕见UnCommon</t>
+  </si>
+  <si>
+    <t>造成10点伤害
+叠加：额外造成6点伤害并对目标施加2层量子坍缩</t>
+  </si>
+  <si>
+    <t>基础伤害+2，叠加额外伤害+2，施加的量子坍缩层数+1</t>
+  </si>
+  <si>
+    <t>量子不确定性</t>
+  </si>
+  <si>
+    <t>能力</t>
+  </si>
+  <si>
+    <t>持有量子叠加时，从卡牌中获得的格挡值额外增加3</t>
+  </si>
+  <si>
+    <t>获得固有</t>
+  </si>
+  <si>
+    <t>开启门扉</t>
+  </si>
+  <si>
+    <t>对所有敌人施加1层虚弱
+叠加：改为对所有敌人施加2层易伤和2层虚弱</t>
+  </si>
+  <si>
+    <t>叠加施加易伤和虚弱层数+1</t>
+  </si>
+  <si>
+    <t>虚弱、易伤</t>
+  </si>
+  <si>
+    <t>粒子波动</t>
+  </si>
+  <si>
+    <t>失去3点生命值
+获得1层量子叠加
+抽2张牌</t>
+  </si>
+  <si>
+    <t>蝶舞</t>
+  </si>
+  <si>
+    <t>造成4点伤害
+触发叠加效果时，将这张牌放入你的手牌</t>
+  </si>
+  <si>
+    <t>羽落映花</t>
+  </si>
+  <si>
+    <t>对所有敌人造成4点伤害
+当前未处于星环爆发状态时，获得1层简并动能</t>
+  </si>
+  <si>
+    <t>伤害增加2，简并动能层数增加1</t>
+  </si>
+  <si>
+    <t>简并动能</t>
+  </si>
+  <si>
+    <t>灵羽沐心</t>
+  </si>
+  <si>
+    <t>你接下来每打出一张攻击牌，获得10层星环能级，可触发4次</t>
+  </si>
+  <si>
+    <t>星环能级增加5</t>
+  </si>
+  <si>
+    <t>星环盈余</t>
+  </si>
+  <si>
+    <t>进入星环爆发状态时，获得25层星环能级
+星环爆发状态下再次进入时不触发</t>
+  </si>
+  <si>
+    <t>获得星环能级增加10</t>
+  </si>
+  <si>
+    <t>春风化雨</t>
+  </si>
+  <si>
+    <t>获得6点格挡
+获得15层星环能级
+叠加：额外获得4点格挡和20层星环能级</t>
+  </si>
+  <si>
+    <t>基础格挡+2，叠加格挡+2，叠加星环能级+10</t>
+  </si>
+  <si>
+    <t>星环爆发，叠加</t>
+  </si>
+  <si>
+    <t>始终如一</t>
+  </si>
+  <si>
+    <t>共鸣攻击造成的伤害增加3</t>
+  </si>
+  <si>
+    <t>共鸣攻击伤害额外+1</t>
+  </si>
+  <si>
+    <t>共鸣攻击</t>
+  </si>
+  <si>
+    <t>监听共鸣攻击只需要在攻击牌打出前或计算伤害时判断是否持有简并动能状态</t>
+  </si>
+  <si>
+    <t>抓捕鸭鸭</t>
+  </si>
+  <si>
+    <t>若目标的意图为攻击，自身获得5层愈合，使目标本回合失去4点力量</t>
+  </si>
+  <si>
+    <t>愈合层数+2，失去力量层数+2</t>
+  </si>
+  <si>
+    <t>愈合，力量</t>
+  </si>
+  <si>
+    <t>白花领域</t>
+  </si>
+  <si>
+    <t>回合开始时，失去1点生命值，获得1点能量</t>
+  </si>
+  <si>
+    <t>能量</t>
+  </si>
+  <si>
+    <t>base.EnergyHoverTip
+能量需描述为能量图标{Amount:energyIcons()}</t>
+  </si>
+  <si>
+    <t>度愈新生</t>
+  </si>
+  <si>
+    <t>获得9层愈合</t>
+  </si>
+  <si>
+    <t>愈合层数+3</t>
+  </si>
+  <si>
+    <t>万灵生息</t>
+  </si>
+  <si>
+    <t>对所有敌人造成相当于愈合层数3倍的伤害
+失去所有愈合层数</t>
+  </si>
+  <si>
+    <t>隧穿效应</t>
+  </si>
+  <si>
+    <t>失去3点生命值
+抽2张牌
+下回合抽1张牌</t>
+  </si>
+  <si>
+    <t>立即抽牌数+1</t>
+  </si>
+  <si>
+    <t>纷扬风翎的邀约</t>
+  </si>
+  <si>
+    <t>下次进入星环爆发状态时，获得2点能量并抽2张牌</t>
+  </si>
+  <si>
+    <t>获得能量+1</t>
+  </si>
+  <si>
+    <t>在星环爆发状态下再次进入星环爆发也生效</t>
+  </si>
+  <si>
+    <t>幻海少女</t>
+  </si>
+  <si>
+    <t>获得1层量子叠加
+下回合获得2点能量</t>
+  </si>
+  <si>
+    <t>量子叠加层数+1，能量+1</t>
+  </si>
+  <si>
+    <t>量子叠加，能量</t>
+  </si>
+  <si>
+    <t>夏花摇曳</t>
+  </si>
+  <si>
+    <t>抽1张牌
+选择一张手牌变化为落英
+叠加：可变化最多3张手牌</t>
+  </si>
+  <si>
+    <t>添加“消耗”和卡牌“落英”的ExtraHoverTip</t>
+  </si>
+  <si>
+    <t>清泉涤愈</t>
+  </si>
+  <si>
+    <t>消耗一张手牌，获得3层愈合</t>
+  </si>
+  <si>
+    <t>愈合层数+2</t>
+  </si>
+  <si>
+    <t>添加“消耗”的ExtraHoverTip</t>
+  </si>
+  <si>
+    <t>光影相携</t>
+  </si>
+  <si>
+    <t>叠加2：获得2点能量，将一张落英加入抽牌堆</t>
+  </si>
+  <si>
+    <t>叠加X</t>
+  </si>
+  <si>
+    <t>能量，落英卡牌</t>
+  </si>
+  <si>
+    <t>生成的牌加入抽牌堆随机位置</t>
+  </si>
+  <si>
+    <t>微光蒙心</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>获得3X层愈合
+对所有敌人施加X层虚弱</t>
+  </si>
+  <si>
+    <t>愈合层数改为4X，虚弱层数改为X+1</t>
+  </si>
+  <si>
+    <t>愈合，虚弱</t>
+  </si>
+  <si>
+    <t>诚勇</t>
+  </si>
+  <si>
+    <t>失去3点生命值
+获得20层星环能级
+获得1层简并动能</t>
+  </si>
+  <si>
+    <t>星环能级+10</t>
+  </si>
+  <si>
+    <t>星环能级，简并动能</t>
+  </si>
+  <si>
+    <t>甘霖回响</t>
+  </si>
+  <si>
+    <t>造成5点伤害
+共鸣：打出后返回手牌</t>
+  </si>
+  <si>
+    <t>伤害+2</t>
+  </si>
+  <si>
+    <t>爱v频道</t>
+  </si>
+  <si>
+    <t>移除目标的格挡。
+施加相当于玩家数量的量子坍缩。</t>
+  </si>
+  <si>
+    <t>添加保留</t>
+  </si>
+  <si>
+    <t>多人游戏限定</t>
+  </si>
+  <si>
+    <t>情报交易</t>
+  </si>
+  <si>
+    <t>使另一名玩家获得9点格挡。
+叠加：额外给予8点格挡。
+共鸣：目标玩家获得1层简并动能</t>
+  </si>
+  <si>
+    <t>基础格挡+3，叠加格挡+3</t>
+  </si>
+  <si>
+    <t>单个队友</t>
+  </si>
+  <si>
+    <t>叠加，共鸣，保留</t>
+  </si>
+  <si>
+    <t>多人游戏限定
+触发共鸣不消耗简并动能</t>
+  </si>
+  <si>
+    <t>绽放</t>
+  </si>
+  <si>
+    <t>对随机敌人造成9点伤害X次
+获得10X点星环能级</t>
+  </si>
+  <si>
+    <t>基础伤害+3，星环能级变为14X</t>
+  </si>
+  <si>
+    <t>飞漾涤痕</t>
+  </si>
+  <si>
+    <t>造成6点伤害3次
+每发动一次共鸣攻击，这张牌在本场战斗中的耗能减少1</t>
+  </si>
+  <si>
+    <t>EnergyCost.AddThisCombat(-1);</t>
+  </si>
+  <si>
+    <t>连理星</t>
+  </si>
+  <si>
+    <t>发动共鸣攻击时，获得1点格挡
+若处于星环爆发状态下，额外获得2点格挡</t>
+  </si>
+  <si>
+    <t>基础格挡+1，爆发格挡+1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>注意能力需要可以叠加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>关键字</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>HoverTips
+HoverTipFactory.FromKeyword(...)</t>
+    </r>
+  </si>
+  <si>
+    <t>抚羽归巢</t>
+  </si>
+  <si>
+    <t>将弃牌堆中最多2张牌加入抽牌堆，使其下次打出免费</t>
+  </si>
+  <si>
+    <t>可选牌数+1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>下次免费打出：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+card.EnergyCost.SetUntilPlayed(0);
+card.SetStarCostUntilPlayed(0);</t>
+    </r>
+  </si>
+  <si>
     <t>恒常誓愿</t>
   </si>
   <si>
     <t>星环爆发状态下，每发动3次共鸣攻击，获得1点能量</t>
+  </si>
+  <si>
+    <t>耗能减少1</t>
   </si>
   <si>
     <t>能量，共鸣</t>
@@ -1126,6 +891,215 @@
     <t>基础伤害和格挡+1，叠加伤害和格挡+1</t>
   </si>
   <si>
+    <t>静谧利刃</t>
+  </si>
+  <si>
+    <t>稀有Rare</t>
+  </si>
+  <si>
+    <t>对随机敌人造成4点伤害3次
+叠加：消耗所有量子叠加层数，每消耗1层对所有敌人造成8点伤害1次</t>
+  </si>
+  <si>
+    <t>叠加造成的群体伤害增加3</t>
+  </si>
+  <si>
+    <t>量子躯体</t>
+  </si>
+  <si>
+    <t>触发叠加效果时，获得4点格挡</t>
+  </si>
+  <si>
+    <t>格挡增加1</t>
+  </si>
+  <si>
+    <t>量子形态</t>
+  </si>
+  <si>
+    <t>回合开始时，获得2层量子叠加。
+每回合首次触发叠加效果时，抽2张牌。</t>
+  </si>
+  <si>
+    <t>量子叠加层数+1，抽牌数+1</t>
+  </si>
+  <si>
+    <t>触发叠加效果可以由SeleeHook实现</t>
+  </si>
+  <si>
+    <t>如晚星，谧引归途</t>
+  </si>
+  <si>
+    <t>进入星环爆发状态</t>
+  </si>
+  <si>
+    <t>星环爆发，消耗</t>
+  </si>
+  <si>
+    <t>此方法进入星环爆发时保留星环能级</t>
+  </si>
+  <si>
+    <t>深海的幻梦</t>
+  </si>
+  <si>
+    <t>发动共鸣攻击时，对所有敌人造成8点伤害</t>
+  </si>
+  <si>
+    <t>伤害增加3</t>
+  </si>
+  <si>
+    <t>暗影洪流</t>
+  </si>
+  <si>
+    <t>对所有敌人造成10点伤害2次
+共鸣：获得2层简并动能</t>
+  </si>
+  <si>
+    <t>良好作息</t>
+  </si>
+  <si>
+    <t>回复相当于愈合层数70%的生命值</t>
+  </si>
+  <si>
+    <t>此牌不会消耗愈合层数</t>
+  </si>
+  <si>
+    <t>晓歌露影</t>
+  </si>
+  <si>
+    <t>目标本回合每受到一次攻击，你获得2层愈合</t>
+  </si>
+  <si>
+    <t>如朝露，消散于晨曦</t>
+  </si>
+  <si>
+    <t>失去6点生命值
+对所有敌人造成21点伤害
+如果此次攻击击杀了敌人，回复6点生命值并再次打出此牌</t>
+  </si>
+  <si>
+    <t>伤害增加7</t>
+  </si>
+  <si>
+    <t>自动打出牌：
+CardCmd.AutoPlay(choiceContext, card, target)
+可持续重复打出直到未能击杀敌人</t>
+  </si>
+  <si>
+    <t>仁术</t>
+  </si>
+  <si>
+    <t>回合开始时，消耗抽牌堆的一张牌，获得3层愈合。
+若消耗的牌为状态或诅咒牌，获得的愈合层数翻倍。</t>
+  </si>
+  <si>
+    <t>在抽牌前触发
+若抽牌堆为空，则不触发消耗效果
+消耗的牌由玩家选择</t>
+  </si>
+  <si>
+    <t>如飞鸟，掠动风漪</t>
+  </si>
+  <si>
+    <t>获得50层星环能级
+抽3张牌</t>
+  </si>
+  <si>
+    <t>七拳碎海</t>
+  </si>
+  <si>
+    <t>接下来的7张攻击牌造成的伤害+2
+其中第7张攻击牌造成的伤害额外+10</t>
+  </si>
+  <si>
+    <t>最后一次攻击伤害+8</t>
+  </si>
+  <si>
+    <t>每打出一张攻击牌算一次攻击，而不是每造成一次伤害
+第7张攻击牌共计+13/21伤害</t>
+  </si>
+  <si>
+    <t>白花郁血</t>
+  </si>
+  <si>
+    <t>在你的回合内，每失去一次生命值，获得3点格挡</t>
+  </si>
+  <si>
+    <t>天坠的星辉</t>
+  </si>
+  <si>
+    <t>对随机敌人造成7点伤害1次
+打出后本场战斗中这张牌的伤害和攻击次数增加1</t>
+  </si>
+  <si>
+    <t>基础攻击次数改为2次</t>
+  </si>
+  <si>
+    <t>诞生=终末</t>
+  </si>
+  <si>
+    <t>对所有敌人造成9点伤害
+使所有量子坍缩状态的敌人失去相当于10%的最大生命值的生命值</t>
+  </si>
+  <si>
+    <t>基础伤害+3，比例增加5%</t>
+  </si>
+  <si>
+    <t>失去生命值效果向下取整，至少为1</t>
+  </si>
+  <si>
+    <t>溯洄海语的摇篮</t>
+  </si>
+  <si>
+    <t>处于星环爆发状态下才可以打出
+对所有敌人造成20点伤害
+结束星环爆发状态，结束前每剩余一层简并动能，获得10层星环能级</t>
+  </si>
+  <si>
+    <t>伤害+8</t>
+  </si>
+  <si>
+    <t>简并动能，星环能级</t>
+  </si>
+  <si>
+    <t>身份互换</t>
+  </si>
+  <si>
+    <t>另一名玩家获得2点能量，抽2张牌
+目标本回合结束时，获得相当于目标格挡值50%的格挡。
+结束你的回合</t>
+  </si>
+  <si>
+    <t>给予能量+1，抽牌+1</t>
+  </si>
+  <si>
+    <t>凋零，只为盛开</t>
+  </si>
+  <si>
+    <t>失去6点生命值
+获得6层愈合
+战斗结束时，回复8点生命值</t>
+  </si>
+  <si>
+    <t>愈合层数+3，回复生命+4</t>
+  </si>
+  <si>
+    <t>战斗结束：
+AfterCombatEnd</t>
+  </si>
+  <si>
+    <t>天秤崩落之刻</t>
+  </si>
+  <si>
+    <t>施加2层量子坍缩
+目标死亡时，对所有其它敌人造成相当于其最大生命值的伤害。</t>
+  </si>
+  <si>
+    <t>耗能减少1，量子坍缩层数+1</t>
+  </si>
+  <si>
+    <t>注意能力需要可以叠加，叠加可造成多倍最大生命值伤害</t>
+  </si>
+  <si>
     <t>永恒=一瞬</t>
   </si>
   <si>
@@ -1176,9 +1150,6 @@
     <t>回合开始时，获得X层愈合，若X的值不小于2则多抽1张牌，若X的值不小于4，则多抽2张牌</t>
   </si>
   <si>
-    <t>抽牌数在叠加能力时获取对应power的对象并增加其动态变量的值以实现叠加。</t>
-  </si>
-  <si>
     <t>如惊霆，锻韧于心</t>
   </si>
   <si>
@@ -1186,6 +1157,42 @@
   </si>
   <si>
     <t>移除消耗</t>
+  </si>
+  <si>
+    <t>魂灵跃动</t>
+  </si>
+  <si>
+    <t>造成6点伤害
+你每失去一次生命值，这张牌在本场战斗中造成的伤害增加3</t>
+  </si>
+  <si>
+    <t>失去生命值时战斗增伤+2</t>
+  </si>
+  <si>
+    <t>化虚为实</t>
+  </si>
+  <si>
+    <t>先古Ancient</t>
+  </si>
+  <si>
+    <t>造成12点伤害
+叠加：额外造成20点伤害并施加2层量子坍缩</t>
+  </si>
+  <si>
+    <t>由坍缩攻击+欧洛巴斯之触变化</t>
+  </si>
+  <si>
+    <t>初醒新芽</t>
+  </si>
+  <si>
+    <t>获得3层量子叠加
+获得2点能量
+获得10层愈合
+获得30层星环能级
+每回合开始时，失去2点生命值</t>
+  </si>
+  <si>
+    <t>量子叠加，能量，星环能级，愈合</t>
   </si>
   <si>
     <t>说明</t>
@@ -1369,6 +1376,9 @@
   </si>
   <si>
     <t>层数表示愈合获得数量，抽牌数由Cards动态变量保存，并由卡牌打出时进行更新</t>
+  </si>
+  <si>
+    <t>触发叠加效果时，对随机敌人造成X点伤害</t>
   </si>
   <si>
     <t>类型/稀有度</t>
@@ -1618,13 +1628,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD2A9F5"/>
+        <fgColor rgb="FFFFFE61"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.6"/>
+        <fgColor rgb="FFD2A9F5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1642,13 +1652,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFE61"/>
+        <fgColor theme="9" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
+        <fgColor theme="9" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2200,19 +2210,19 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2267,7 +2277,12 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2558,7 +2573,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K88"/>
+  <dimension ref="A1:K89"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="19.0909090909091" style="7" customWidth="1"/>
@@ -2729,18 +2744,18 @@
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
     </row>
-    <row r="6" ht="28" spans="1:11">
+    <row r="6" spans="1:11">
       <c r="A6" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B6" s="14">
-        <v>1</v>
-      </c>
-      <c r="C6" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>32</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>33</v>
@@ -2752,34 +2767,34 @@
         <v>16</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I6" s="2"/>
       <c r="J6" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" ht="28" spans="1:11">
-      <c r="A7" s="17" t="s">
-        <v>37</v>
+      <c r="A7" s="18" t="s">
+        <v>38</v>
       </c>
       <c r="B7" s="14">
         <v>1</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D7" s="14" t="s">
         <v>19</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>22</v>
@@ -2792,23 +2807,23 @@
       <c r="K7" s="3"/>
     </row>
     <row r="8" ht="28" spans="1:11">
-      <c r="A8" s="17" t="s">
-        <v>41</v>
+      <c r="A8" s="18" t="s">
+        <v>42</v>
       </c>
       <c r="B8" s="14">
         <v>1</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D8" s="14" t="s">
         <v>13</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>16</v>
@@ -2823,23 +2838,23 @@
       <c r="K8" s="3"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="17" t="s">
-        <v>44</v>
+      <c r="A9" s="18" t="s">
+        <v>45</v>
       </c>
       <c r="B9" s="14">
         <v>1</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" s="14" t="s">
         <v>19</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>22</v>
@@ -2852,23 +2867,23 @@
       <c r="K9" s="3"/>
     </row>
     <row r="10" ht="42" spans="1:11">
-      <c r="A10" s="17" t="s">
-        <v>47</v>
+      <c r="A10" s="18" t="s">
+        <v>48</v>
       </c>
       <c r="B10" s="14">
         <v>2</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D10" s="14" t="s">
         <v>19</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>22</v>
@@ -2880,18 +2895,18 @@
       </c>
       <c r="K10" s="3"/>
     </row>
-    <row r="11" ht="42" spans="1:11">
-      <c r="A11" s="17" t="s">
-        <v>50</v>
+    <row r="11" spans="1:11">
+      <c r="A11" s="19" t="s">
+        <v>51</v>
       </c>
       <c r="B11" s="14">
         <v>1</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>52</v>
@@ -2900,95 +2915,95 @@
         <v>53</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="3" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="K11" s="3"/>
     </row>
     <row r="12" ht="28" spans="1:11">
-      <c r="A12" s="17" t="s">
-        <v>54</v>
+      <c r="A12" s="19" t="s">
+        <v>56</v>
       </c>
       <c r="B12" s="14">
         <v>1</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H12" s="16"/>
+        <v>16</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="I12" s="2"/>
-      <c r="J12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" ht="42" spans="1:11">
-      <c r="A13" s="17" t="s">
-        <v>58</v>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" ht="28" spans="1:11">
+      <c r="A13" s="19" t="s">
+        <v>61</v>
       </c>
       <c r="B13" s="14">
         <v>1</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="I13" s="2"/>
-      <c r="J13" s="3" t="s">
-        <v>62</v>
-      </c>
+      <c r="J13" s="3"/>
       <c r="K13" s="3"/>
     </row>
-    <row r="14" ht="42" spans="1:11">
-      <c r="A14" s="17" t="s">
-        <v>63</v>
+    <row r="14" spans="1:11">
+      <c r="A14" s="20" t="s">
+        <v>65</v>
       </c>
       <c r="B14" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>19</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>22</v>
@@ -2996,232 +3011,224 @@
       <c r="H14" s="16"/>
       <c r="I14" s="2"/>
       <c r="J14" s="3" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="K14" s="3"/>
     </row>
     <row r="15" ht="28" spans="1:11">
-      <c r="A15" s="17" t="s">
-        <v>65</v>
+      <c r="A15" s="20" t="s">
+        <v>69</v>
       </c>
       <c r="B15" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H15" s="16" t="s">
-        <v>30</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="H15" s="16"/>
       <c r="I15" s="2"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
     </row>
-    <row r="16" ht="42" spans="1:11">
-      <c r="A16" s="17" t="s">
-        <v>68</v>
+    <row r="16" ht="28" spans="1:11">
+      <c r="A16" s="20" t="s">
+        <v>72</v>
       </c>
       <c r="B16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D16" s="14" t="s">
         <v>13</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H16" s="16" t="s">
-        <v>30</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="H16" s="16"/>
       <c r="I16" s="2"/>
-      <c r="J16" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="J16" s="3"/>
       <c r="K16" s="3"/>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" ht="28" spans="1:11">
       <c r="A17" s="17" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B17" s="14">
         <v>1</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I17" s="2"/>
-      <c r="J17" s="3"/>
+      <c r="J17" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="K17" s="3"/>
     </row>
     <row r="18" ht="28" spans="1:11">
       <c r="A18" s="17" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B18" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H18" s="16" t="s">
         <v>30</v>
       </c>
       <c r="I18" s="2"/>
-      <c r="J18" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" s="19" t="s">
-        <v>79</v>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+    </row>
+    <row r="19" ht="28" spans="1:11">
+      <c r="A19" s="17" t="s">
+        <v>82</v>
       </c>
       <c r="B19" s="14">
         <v>1</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D19" s="14" t="s">
         <v>19</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="3" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="K19" s="3"/>
     </row>
     <row r="20" ht="28" spans="1:11">
-      <c r="A20" s="19" t="s">
-        <v>84</v>
+      <c r="A20" s="17" t="s">
+        <v>85</v>
       </c>
       <c r="B20" s="14">
         <v>1</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H20" s="16" t="s">
-        <v>87</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="H20" s="16"/>
       <c r="I20" s="2"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>88</v>
       </c>
+      <c r="K20" s="3"/>
     </row>
     <row r="21" ht="28" spans="1:11">
       <c r="A21" s="19" t="s">
         <v>89</v>
       </c>
       <c r="B21" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>90</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="I21" s="2"/>
-      <c r="J21" s="3"/>
+      <c r="J21" s="3" t="s">
+        <v>55</v>
+      </c>
       <c r="K21" s="3"/>
     </row>
     <row r="22" ht="42" spans="1:11">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="18" t="s">
         <v>92</v>
       </c>
       <c r="B22" s="14">
         <v>1</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="D22" s="14" t="s">
         <v>13</v>
@@ -3233,10 +3240,10 @@
         <v>94</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="I22" s="2"/>
       <c r="J22" s="3" t="s">
@@ -3245,14 +3252,14 @@
       <c r="K22" s="3"/>
     </row>
     <row r="23" ht="28" spans="1:11">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="20" t="s">
         <v>96</v>
       </c>
       <c r="B23" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="D23" s="14" t="s">
         <v>19</v>
@@ -3266,47 +3273,43 @@
       <c r="G23" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H23" s="16" t="s">
-        <v>82</v>
-      </c>
+      <c r="H23" s="16"/>
       <c r="I23" s="2"/>
       <c r="J23" s="3" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="K23" s="3"/>
     </row>
     <row r="24" ht="28" spans="1:11">
-      <c r="A24" s="19" t="s">
+      <c r="A24" s="18" t="s">
         <v>99</v>
       </c>
       <c r="B24" s="14">
         <v>1</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>100</v>
       </c>
       <c r="F24" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="G24" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="H24" s="16" t="s">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="I24" s="2"/>
-      <c r="J24" s="3" t="s">
-        <v>83</v>
-      </c>
+      <c r="J24" s="3"/>
       <c r="K24" s="3"/>
     </row>
-    <row r="25" ht="42" spans="1:11">
+    <row r="25" ht="58" spans="1:11">
       <c r="A25" s="19" t="s">
         <v>102</v>
       </c>
@@ -3314,7 +3317,7 @@
         <v>1</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="D25" s="14" t="s">
         <v>19</v>
@@ -3328,58 +3331,58 @@
       <c r="G25" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H25" s="16" t="s">
-        <v>105</v>
-      </c>
+      <c r="H25" s="16"/>
       <c r="I25" s="2"/>
       <c r="J25" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="K25" s="3"/>
+        <v>105</v>
+      </c>
+      <c r="K25" s="21" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="26" ht="28" spans="1:11">
-      <c r="A26" s="19" t="s">
-        <v>106</v>
+      <c r="A26" s="20" t="s">
+        <v>107</v>
       </c>
       <c r="B26" s="14">
         <v>1</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H26" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="I26" s="2"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" s="16"/>
+      <c r="I26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="K26" s="3"/>
+    </row>
+    <row r="27" ht="42" spans="1:11">
+      <c r="A27" s="18" t="s">
         <v>110</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" s="19" t="s">
-        <v>111</v>
       </c>
       <c r="B27" s="14">
         <v>1</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>112</v>
@@ -3388,95 +3391,95 @@
         <v>113</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H27" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="I27" s="2"/>
+      <c r="J27" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K27" s="3"/>
+    </row>
+    <row r="28" ht="28" spans="1:11">
+      <c r="A28" s="18" t="s">
         <v>114</v>
-      </c>
-      <c r="I27" s="2"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
-      <c r="A28" s="19" t="s">
-        <v>116</v>
       </c>
       <c r="B28" s="14">
         <v>1</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>55</v>
+        <v>115</v>
       </c>
       <c r="E28" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F28" s="15" t="s">
         <v>117</v>
-      </c>
-      <c r="F28" s="15" t="s">
-        <v>118</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H28" s="16" t="s">
-        <v>109</v>
-      </c>
+      <c r="H28" s="16"/>
       <c r="I28" s="2"/>
-      <c r="J28" s="3"/>
+      <c r="J28" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="K28" s="3"/>
     </row>
-    <row r="29" ht="28" spans="1:11">
-      <c r="A29" s="19" t="s">
+    <row r="29" ht="42" spans="1:11">
+      <c r="A29" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="B29" s="14">
+        <v>1</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E29" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B29" s="14">
-        <v>2</v>
-      </c>
-      <c r="C29" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="D29" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E29" s="3" t="s">
+      <c r="F29" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="F29" s="15" t="s">
-        <v>86</v>
-      </c>
       <c r="G29" s="2" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>91</v>
+        <v>30</v>
       </c>
       <c r="I29" s="2"/>
       <c r="J29" s="3" t="s">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="K29" s="3"/>
     </row>
-    <row r="30" spans="1:11">
-      <c r="A30" s="20" t="s">
-        <v>121</v>
+    <row r="30" ht="42" spans="1:11">
+      <c r="A30" s="18" t="s">
+        <v>122</v>
       </c>
       <c r="B30" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="D30" s="14" t="s">
         <v>19</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>123</v>
+        <v>47</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>22</v>
@@ -3484,344 +3487,350 @@
       <c r="H30" s="16"/>
       <c r="I30" s="2"/>
       <c r="J30" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K30" s="3"/>
+    </row>
+    <row r="31" ht="28" spans="1:11">
+      <c r="A31" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="K30" s="3"/>
-    </row>
-    <row r="31" ht="28" spans="1:11">
-      <c r="A31" s="20" t="s">
+      <c r="B31" s="14">
+        <v>0</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B31" s="14">
-        <v>1</v>
-      </c>
-      <c r="C31" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>126</v>
-      </c>
       <c r="F31" s="15" t="s">
-        <v>127</v>
+        <v>63</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H31" s="16"/>
+        <v>16</v>
+      </c>
+      <c r="H31" s="16" t="s">
+        <v>30</v>
+      </c>
       <c r="I31" s="2"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
     </row>
-    <row r="32" ht="28" spans="1:11">
-      <c r="A32" s="20" t="s">
-        <v>128</v>
+    <row r="32" ht="42" spans="1:11">
+      <c r="A32" s="19" t="s">
+        <v>126</v>
       </c>
       <c r="B32" s="14">
         <v>1</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="D32" s="14" t="s">
         <v>13</v>
       </c>
       <c r="E32" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F32" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H32" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="I32" s="2"/>
+      <c r="J32" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="F32" s="15" t="s">
+      <c r="K32" s="3"/>
+    </row>
+    <row r="33" ht="28" spans="1:11">
+      <c r="A33" s="19" t="s">
         <v>130</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="H32" s="16"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
-    </row>
-    <row r="33" ht="28" spans="1:11">
-      <c r="A33" s="20" t="s">
-        <v>132</v>
       </c>
       <c r="B33" s="14">
         <v>1</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>51</v>
+        <v>111</v>
       </c>
       <c r="D33" s="14" t="s">
         <v>19</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F33" s="15" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H33" s="16"/>
+        <v>22</v>
+      </c>
+      <c r="H33" s="16" t="s">
+        <v>54</v>
+      </c>
       <c r="I33" s="2"/>
       <c r="J33" s="3" t="s">
-        <v>135</v>
+        <v>55</v>
       </c>
       <c r="K33" s="3"/>
     </row>
-    <row r="34" ht="42" spans="1:11">
-      <c r="A34" s="20" t="s">
-        <v>136</v>
+    <row r="34" ht="28" spans="1:11">
+      <c r="A34" s="19" t="s">
+        <v>133</v>
       </c>
       <c r="B34" s="14">
         <v>1</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>51</v>
+        <v>111</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>55</v>
+        <v>115</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F34" s="15" t="s">
-        <v>57</v>
+        <v>135</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H34" s="16"/>
+      <c r="H34" s="16" t="s">
+        <v>54</v>
+      </c>
       <c r="I34" s="2"/>
       <c r="J34" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
-      <c r="A35" s="20" t="s">
-        <v>140</v>
+        <v>55</v>
+      </c>
+      <c r="K34" s="3"/>
+    </row>
+    <row r="35" ht="42" spans="1:11">
+      <c r="A35" s="19" t="s">
+        <v>136</v>
       </c>
       <c r="B35" s="14">
         <v>1</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>51</v>
+        <v>111</v>
       </c>
       <c r="D35" s="14" t="s">
         <v>19</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F35" s="15" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="16" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="I35" s="2"/>
       <c r="J35" s="3" t="s">
-        <v>124</v>
+        <v>55</v>
       </c>
       <c r="K35" s="3"/>
     </row>
     <row r="36" ht="28" spans="1:11">
-      <c r="A36" s="20" t="s">
-        <v>144</v>
+      <c r="A36" s="19" t="s">
+        <v>140</v>
       </c>
       <c r="B36" s="14">
         <v>1</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>51</v>
+        <v>111</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>13</v>
+        <v>115</v>
       </c>
       <c r="E36" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="F36" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H36" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="I36" s="2"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="37" ht="28" spans="1:11">
+      <c r="A37" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="F36" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H36" s="16"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="K36" s="3"/>
-    </row>
-    <row r="37" ht="42" spans="1:11">
-      <c r="A37" s="20" t="s">
-        <v>146</v>
-      </c>
       <c r="B37" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>51</v>
+        <v>111</v>
       </c>
       <c r="D37" s="14" t="s">
         <v>19</v>
       </c>
       <c r="E37" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="F37" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="F37" s="15" t="s">
-        <v>148</v>
-      </c>
       <c r="G37" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H37" s="16"/>
       <c r="I37" s="2"/>
-      <c r="J37" s="3"/>
+      <c r="J37" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="K37" s="3"/>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" ht="42" spans="1:11">
       <c r="A38" s="20" t="s">
         <v>149</v>
       </c>
       <c r="B38" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>150</v>
       </c>
       <c r="F38" s="15" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H38" s="16" t="s">
-        <v>143</v>
-      </c>
+      <c r="H38" s="16"/>
       <c r="I38" s="2"/>
       <c r="J38" s="3" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="20" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B39" s="14">
         <v>1</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="D39" s="14" t="s">
         <v>19</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F39" s="15" t="s">
-        <v>113</v>
+        <v>155</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H39" s="16"/>
+        <v>22</v>
+      </c>
+      <c r="H39" s="16" t="s">
+        <v>35</v>
+      </c>
       <c r="I39" s="2"/>
       <c r="J39" s="3" t="s">
-        <v>124</v>
+        <v>68</v>
       </c>
       <c r="K39" s="3"/>
     </row>
-    <row r="40" ht="56" spans="1:11">
+    <row r="40" ht="28" spans="1:11">
       <c r="A40" s="20" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B40" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="D40" s="14" t="s">
         <v>13</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F40" s="15" t="s">
-        <v>156</v>
+        <v>34</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H40" s="16" t="s">
-        <v>143</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="H40" s="16"/>
       <c r="I40" s="2"/>
-      <c r="J40" s="3"/>
-      <c r="K40" s="3" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="41" ht="56" spans="1:11">
+      <c r="J40" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="K40" s="3"/>
+    </row>
+    <row r="41" ht="42" spans="1:11">
       <c r="A41" s="20" t="s">
         <v>158</v>
       </c>
       <c r="B41" s="14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>159</v>
       </c>
       <c r="F41" s="15" t="s">
-        <v>34</v>
+        <v>160</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H41" s="16"/>
       <c r="I41" s="2"/>
-      <c r="J41" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>160</v>
-      </c>
+      <c r="J41" s="3"/>
+      <c r="K41" s="3"/>
     </row>
     <row r="42" ht="28" spans="1:11">
-      <c r="A42" s="21" t="s">
+      <c r="A42" s="17" t="s">
         <v>161</v>
       </c>
       <c r="B42" s="14">
         <v>1</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="D42" s="14" t="s">
         <v>19</v>
@@ -3836,1153 +3845,1151 @@
         <v>22</v>
       </c>
       <c r="H42" s="16" t="s">
-        <v>143</v>
+        <v>54</v>
       </c>
       <c r="I42" s="2"/>
       <c r="J42" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K42" s="3"/>
+        <v>151</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="43" ht="28" spans="1:11">
-      <c r="A43" s="21" t="s">
-        <v>164</v>
+      <c r="A43" s="17" t="s">
+        <v>165</v>
       </c>
       <c r="B43" s="14">
         <v>1</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F43" s="15" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H43" s="16" t="s">
-        <v>30</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="H43" s="16"/>
       <c r="I43" s="2"/>
-      <c r="J43" s="3"/>
+      <c r="J43" s="3" t="s">
+        <v>168</v>
+      </c>
       <c r="K43" s="3"/>
     </row>
-    <row r="44" ht="28" spans="1:11">
-      <c r="A44" s="21" t="s">
-        <v>167</v>
+    <row r="44" ht="42" spans="1:11">
+      <c r="A44" s="17" t="s">
+        <v>169</v>
       </c>
       <c r="B44" s="14">
         <v>1</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="D44" s="14" t="s">
         <v>19</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F44" s="15" t="s">
-        <v>169</v>
+        <v>78</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H44" s="16" t="s">
-        <v>82</v>
-      </c>
+      <c r="H44" s="16"/>
       <c r="I44" s="2"/>
-      <c r="J44" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="K44" s="3"/>
-    </row>
-    <row r="45" ht="28" spans="1:11">
-      <c r="A45" s="21" t="s">
-        <v>170</v>
+      <c r="J44" s="3"/>
+      <c r="K44" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" s="17" t="s">
+        <v>172</v>
       </c>
       <c r="B45" s="14">
         <v>1</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>51</v>
+        <v>111</v>
       </c>
       <c r="D45" s="14" t="s">
         <v>19</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F45" s="15" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H45" s="16" t="s">
-        <v>82</v>
-      </c>
+      <c r="H45" s="16"/>
       <c r="I45" s="2"/>
       <c r="J45" s="3" t="s">
-        <v>138</v>
+        <v>68</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="46" ht="28" spans="1:11">
-      <c r="A46" s="21" t="s">
-        <v>174</v>
+      <c r="A46" s="17" t="s">
+        <v>176</v>
       </c>
       <c r="B46" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>51</v>
+        <v>111</v>
       </c>
       <c r="D46" s="14" t="s">
         <v>19</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F46" s="15" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H46" s="16"/>
+      <c r="H46" s="16" t="s">
+        <v>178</v>
+      </c>
       <c r="I46" s="2"/>
       <c r="J46" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="K46" s="3"/>
-    </row>
-    <row r="47" ht="42" spans="1:11">
-      <c r="A47" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="B47" s="14">
-        <v>1</v>
+        <v>179</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="47" ht="28" spans="1:11">
+      <c r="A47" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="B47" s="14" t="s">
+        <v>182</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>51</v>
+        <v>111</v>
       </c>
       <c r="D47" s="14" t="s">
         <v>19</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="F47" s="15" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>22</v>
+        <v>101</v>
       </c>
       <c r="H47" s="16"/>
       <c r="I47" s="2"/>
-      <c r="J47" s="3"/>
-      <c r="K47" s="3" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11">
-      <c r="A48" s="21" t="s">
-        <v>181</v>
+      <c r="J47" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="K47" s="3"/>
+    </row>
+    <row r="48" ht="42" spans="1:11">
+      <c r="A48" s="19" t="s">
+        <v>186</v>
       </c>
       <c r="B48" s="14">
         <v>0</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>182</v>
+        <v>111</v>
       </c>
       <c r="D48" s="14" t="s">
         <v>19</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F48" s="15" t="s">
-        <v>113</v>
+        <v>188</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H48" s="16" t="s">
-        <v>143</v>
+        <v>54</v>
       </c>
       <c r="I48" s="2"/>
       <c r="J48" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11">
-      <c r="A49" s="21" t="s">
-        <v>185</v>
+        <v>189</v>
+      </c>
+      <c r="K48" s="3"/>
+    </row>
+    <row r="49" ht="28" spans="1:11">
+      <c r="A49" s="19" t="s">
+        <v>190</v>
       </c>
       <c r="B49" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>51</v>
+        <v>111</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="F49" s="15" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H49" s="16"/>
+      <c r="H49" s="16" t="s">
+        <v>64</v>
+      </c>
       <c r="I49" s="2"/>
-      <c r="J49" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>188</v>
-      </c>
+      <c r="J49" s="3"/>
+      <c r="K49" s="3"/>
     </row>
     <row r="50" ht="28" spans="1:11">
-      <c r="A50" s="21" t="s">
-        <v>189</v>
+      <c r="A50" s="22" t="s">
+        <v>193</v>
       </c>
       <c r="B50" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="D50" s="14" t="s">
         <v>19</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="F50" s="15" t="s">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H50" s="16" t="s">
-        <v>143</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="H50" s="16"/>
       <c r="I50" s="2"/>
       <c r="J50" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="K50" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="51" ht="42" spans="1:11">
-      <c r="A51" s="21" t="s">
-        <v>191</v>
+      <c r="A51" s="22" t="s">
+        <v>197</v>
       </c>
       <c r="B51" s="14">
         <v>1</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="D51" s="14" t="s">
         <v>19</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="F51" s="15" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H51" s="16"/>
+        <v>200</v>
+      </c>
+      <c r="H51" s="16" t="s">
+        <v>201</v>
+      </c>
       <c r="I51" s="2"/>
-      <c r="J51" s="3"/>
+      <c r="J51" s="3" t="s">
+        <v>129</v>
+      </c>
       <c r="K51" s="3" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
     </row>
     <row r="52" ht="28" spans="1:11">
-      <c r="A52" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="B52" s="14">
-        <v>1</v>
+      <c r="A52" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="B52" s="14" t="s">
+        <v>182</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="F52" s="15" t="s">
-        <v>74</v>
+        <v>205</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="H52" s="16"/>
       <c r="I52" s="2"/>
       <c r="J52" s="3"/>
       <c r="K52" s="3"/>
     </row>
-    <row r="53" ht="28" spans="1:11">
-      <c r="A53" s="21" t="s">
-        <v>197</v>
+    <row r="53" ht="42" spans="1:11">
+      <c r="A53" s="19" t="s">
+        <v>206</v>
       </c>
       <c r="B53" s="14">
+        <v>3</v>
+      </c>
+      <c r="C53" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="D53" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F53" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H53" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="I53" s="2"/>
+      <c r="J53" s="3"/>
+      <c r="K53" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="54" ht="43.5" spans="1:11">
+      <c r="A54" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="B54" s="14">
         <v>1</v>
       </c>
-      <c r="C53" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="D53" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="F53" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H53" s="16"/>
-      <c r="I53" s="2"/>
-      <c r="J53" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="K53" s="3"/>
-    </row>
-    <row r="54" ht="28" spans="1:11">
-      <c r="A54" s="19" t="s">
-        <v>201</v>
-      </c>
-      <c r="B54" s="14">
-        <v>0</v>
-      </c>
       <c r="C54" s="14" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="F54" s="15" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H54" s="16" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="I54" s="2"/>
       <c r="J54" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="K54" s="3"/>
-    </row>
-    <row r="55" ht="28" spans="1:11">
-      <c r="A55" s="21" t="s">
-        <v>204</v>
+        <v>64</v>
+      </c>
+      <c r="K54" s="21" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="55" ht="43.5" spans="1:11">
+      <c r="A55" s="17" t="s">
+        <v>213</v>
       </c>
       <c r="B55" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>51</v>
+        <v>111</v>
       </c>
       <c r="D55" s="14" t="s">
         <v>19</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="F55" s="15" t="s">
-        <v>172</v>
+        <v>215</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H55" s="16" t="s">
-        <v>206</v>
+        <v>35</v>
       </c>
       <c r="I55" s="2"/>
-      <c r="J55" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="K55" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="56" ht="42" spans="1:11">
-      <c r="A56" s="21" t="s">
-        <v>209</v>
+      <c r="J55" s="3"/>
+      <c r="K55" s="23" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="56" ht="28" spans="1:11">
+      <c r="A56" s="19" t="s">
+        <v>217</v>
       </c>
       <c r="B56" s="14">
         <v>1</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>13</v>
+        <v>115</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="F56" s="15" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="H56" s="16"/>
+        <v>22</v>
+      </c>
+      <c r="H56" s="16" t="s">
+        <v>54</v>
+      </c>
       <c r="I56" s="2"/>
-      <c r="J56" s="3"/>
+      <c r="J56" s="3" t="s">
+        <v>220</v>
+      </c>
       <c r="K56" s="3"/>
     </row>
-    <row r="57" ht="42" spans="1:11">
-      <c r="A57" s="17" t="s">
-        <v>212</v>
+    <row r="57" spans="1:11">
+      <c r="A57" s="18" t="s">
+        <v>221</v>
       </c>
       <c r="B57" s="14">
         <v>1</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>13</v>
+        <v>115</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="F57" s="15" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="H57" s="16"/>
       <c r="I57" s="2"/>
       <c r="J57" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="58" ht="28" spans="1:11">
-      <c r="A58" s="20" t="s">
-        <v>216</v>
-      </c>
-      <c r="B58" s="14" t="s">
-        <v>217</v>
+        <v>26</v>
+      </c>
+      <c r="K57" s="3"/>
+    </row>
+    <row r="58" spans="1:11">
+      <c r="A58" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="B58" s="14">
+        <v>2</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>51</v>
+        <v>111</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F58" s="15" t="s">
         <v>219</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="H58" s="16"/>
       <c r="I58" s="2"/>
       <c r="J58" s="3" t="s">
-        <v>220</v>
+        <v>30</v>
       </c>
       <c r="K58" s="3"/>
     </row>
-    <row r="59" ht="56" spans="1:11">
-      <c r="A59" s="19" t="s">
-        <v>221</v>
+    <row r="59" spans="1:11">
+      <c r="A59" s="18" t="s">
+        <v>225</v>
       </c>
       <c r="B59" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>13</v>
+        <v>115</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F59" s="15" t="s">
-        <v>223</v>
+        <v>63</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H59" s="16" t="s">
-        <v>82</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="H59" s="16"/>
       <c r="I59" s="2"/>
       <c r="J59" s="3" t="s">
-        <v>224</v>
+        <v>30</v>
       </c>
       <c r="K59" s="3"/>
     </row>
-    <row r="60" ht="70" spans="1:11">
-      <c r="A60" s="21" t="s">
-        <v>225</v>
+    <row r="60" ht="42" spans="1:11">
+      <c r="A60" s="20" t="s">
+        <v>227</v>
       </c>
       <c r="B60" s="14">
-        <v>0</v>
-      </c>
-      <c r="C60" s="18" t="s">
-        <v>32</v>
+        <v>1</v>
+      </c>
+      <c r="C60" s="14" t="s">
+        <v>111</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F60" s="15" t="s">
-        <v>57</v>
+        <v>229</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="H60" s="16"/>
       <c r="I60" s="2"/>
       <c r="J60" s="3" t="s">
-        <v>227</v>
+        <v>68</v>
       </c>
       <c r="K60" s="3"/>
     </row>
-    <row r="61" ht="42" spans="1:11">
-      <c r="A61" s="17" t="s">
-        <v>228</v>
+    <row r="61" ht="28" spans="1:11">
+      <c r="A61" s="18" t="s">
+        <v>230</v>
       </c>
       <c r="B61" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="D61" s="14" t="s">
         <v>13</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F61" s="15" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H61" s="16" t="s">
-        <v>30</v>
+        <v>178</v>
       </c>
       <c r="I61" s="2"/>
-      <c r="J61" s="3" t="s">
-        <v>231</v>
-      </c>
+      <c r="J61" s="3"/>
       <c r="K61" s="3"/>
     </row>
-    <row r="62" ht="28" spans="1:11">
-      <c r="A62" s="20" t="s">
-        <v>232</v>
+    <row r="62" ht="42" spans="1:11">
+      <c r="A62" s="18" t="s">
+        <v>233</v>
       </c>
       <c r="B62" s="14">
         <v>0</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F62" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H62" s="16"/>
+        <v>16</v>
+      </c>
+      <c r="H62" s="16" t="s">
+        <v>30</v>
+      </c>
       <c r="I62" s="2"/>
-      <c r="J62" s="3" t="s">
-        <v>124</v>
-      </c>
+      <c r="J62" s="3"/>
       <c r="K62" s="3"/>
     </row>
     <row r="63" ht="42" spans="1:11">
-      <c r="A63" s="19" t="s">
-        <v>235</v>
+      <c r="A63" s="18" t="s">
+        <v>236</v>
       </c>
       <c r="B63" s="14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C63" s="14" t="s">
-        <v>51</v>
+        <v>237</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F63" s="15" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>22</v>
+        <v>101</v>
       </c>
       <c r="H63" s="16" t="s">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="I63" s="2"/>
       <c r="J63" s="3" t="s">
-        <v>238</v>
+        <v>26</v>
       </c>
       <c r="K63" s="3"/>
     </row>
-    <row r="64" ht="28" spans="1:11">
-      <c r="A64" s="19" t="s">
-        <v>239</v>
+    <row r="64" spans="1:11">
+      <c r="A64" s="18" t="s">
+        <v>240</v>
       </c>
       <c r="B64" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>51</v>
+        <v>237</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>13</v>
+        <v>115</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F64" s="15" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H64" s="16" t="s">
-        <v>91</v>
+        <v>30</v>
       </c>
       <c r="I64" s="2"/>
       <c r="J64" s="3"/>
       <c r="K64" s="3"/>
     </row>
     <row r="65" ht="28" spans="1:11">
-      <c r="A65" s="22" t="s">
-        <v>242</v>
+      <c r="A65" s="18" t="s">
+        <v>243</v>
       </c>
       <c r="B65" s="14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C65" s="14" t="s">
-        <v>51</v>
+        <v>237</v>
       </c>
       <c r="D65" s="14" t="s">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F65" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H65" s="16"/>
+        <v>22</v>
+      </c>
+      <c r="H65" s="16" t="s">
+        <v>30</v>
+      </c>
       <c r="I65" s="2"/>
       <c r="J65" s="3" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="66" ht="42" spans="1:11">
-      <c r="A66" s="22" t="s">
         <v>246</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11">
+      <c r="A66" s="19" t="s">
+        <v>247</v>
       </c>
       <c r="B66" s="14">
         <v>1</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>51</v>
+        <v>237</v>
       </c>
       <c r="D66" s="14" t="s">
         <v>19</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F66" s="15" t="s">
-        <v>248</v>
+        <v>34</v>
       </c>
       <c r="G66" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H66" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="H66" s="16" t="s">
+      <c r="I66" s="2"/>
+      <c r="J66" s="3"/>
+      <c r="K66" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="I66" s="2"/>
-      <c r="J66" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="K66" s="3" t="s">
+    </row>
+    <row r="67" spans="1:11">
+      <c r="A67" s="19" t="s">
         <v>251</v>
-      </c>
-    </row>
-    <row r="67" ht="56" spans="1:11">
-      <c r="A67" s="22" t="s">
-        <v>252</v>
       </c>
       <c r="B67" s="14">
         <v>1</v>
       </c>
       <c r="C67" s="14" t="s">
-        <v>69</v>
+        <v>237</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="E67" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="F67" s="15" t="s">
         <v>253</v>
       </c>
-      <c r="F67" s="15" t="s">
-        <v>254</v>
-      </c>
       <c r="G67" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="H67" s="16"/>
+        <v>22</v>
+      </c>
+      <c r="H67" s="16" t="s">
+        <v>143</v>
+      </c>
       <c r="I67" s="2"/>
-      <c r="J67" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="K67" s="3" t="s">
-        <v>245</v>
-      </c>
+      <c r="J67" s="3"/>
+      <c r="K67" s="3"/>
     </row>
     <row r="68" ht="28" spans="1:11">
       <c r="A68" s="19" t="s">
-        <v>255</v>
-      </c>
-      <c r="B68" s="14" t="s">
-        <v>217</v>
+        <v>254</v>
+      </c>
+      <c r="B68" s="14">
+        <v>2</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>51</v>
+        <v>237</v>
       </c>
       <c r="D68" s="14" t="s">
         <v>13</v>
       </c>
       <c r="E68" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="F68" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H68" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="I68" s="2"/>
+      <c r="J68" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="K68" s="3"/>
+    </row>
+    <row r="69" spans="1:11">
+      <c r="A69" s="20" t="s">
         <v>256</v>
       </c>
-      <c r="F68" s="15" t="s">
+      <c r="B69" s="14">
+        <v>2</v>
+      </c>
+      <c r="C69" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="D69" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E69" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="G68" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="H68" s="16"/>
-      <c r="I68" s="2"/>
-      <c r="J68" s="3"/>
-      <c r="K68" s="3"/>
-    </row>
-    <row r="69" ht="28" spans="1:11">
-      <c r="A69" s="17" t="s">
+      <c r="F69" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H69" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="I69" s="2"/>
+      <c r="J69" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="K69" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="B69" s="14">
+    </row>
+    <row r="70" spans="1:11">
+      <c r="A70" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="B70" s="14">
         <v>1</v>
       </c>
-      <c r="C69" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="D69" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="F69" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H69" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="I69" s="2"/>
-      <c r="J69" s="3"/>
-      <c r="K69" s="3"/>
-    </row>
-    <row r="70" ht="42" spans="1:11">
-      <c r="A70" s="19" t="s">
+      <c r="C70" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="D70" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E70" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="B70" s="14">
-        <v>3</v>
-      </c>
-      <c r="C70" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D70" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>261</v>
-      </c>
       <c r="F70" s="15" t="s">
-        <v>241</v>
+        <v>34</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H70" s="16" t="s">
-        <v>91</v>
-      </c>
+      <c r="H70" s="16"/>
       <c r="I70" s="2"/>
-      <c r="J70" s="3"/>
-      <c r="K70" s="3" t="s">
+      <c r="J70" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="K70" s="3"/>
+    </row>
+    <row r="71" ht="56" spans="1:11">
+      <c r="A71" s="20" t="s">
+        <v>261</v>
+      </c>
+      <c r="B71" s="14">
+        <v>2</v>
+      </c>
+      <c r="C71" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="D71" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E71" s="3" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="71" ht="42" spans="1:11">
-      <c r="A71" s="20" t="s">
+      <c r="F71" s="15" t="s">
         <v>263</v>
       </c>
-      <c r="B71" s="14">
-        <v>1</v>
-      </c>
-      <c r="C71" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="D71" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="E71" s="3" t="s">
+      <c r="G71" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H71" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="I71" s="2"/>
+      <c r="J71" s="3"/>
+      <c r="K71" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="F71" s="15" t="s">
+    </row>
+    <row r="72" ht="56" spans="1:11">
+      <c r="A72" s="20" t="s">
         <v>265</v>
       </c>
-      <c r="G71" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H71" s="16"/>
-      <c r="I71" s="2"/>
-      <c r="J71" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="K71" s="3" t="s">
+      <c r="B72" s="14">
+        <v>2</v>
+      </c>
+      <c r="C72" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="D72" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="E72" s="3" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="72" ht="43.5" spans="1:11">
-      <c r="A72" s="19" t="s">
-        <v>267</v>
-      </c>
-      <c r="B72" s="14">
-        <v>1</v>
-      </c>
-      <c r="C72" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D72" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>268</v>
-      </c>
       <c r="F72" s="3" t="s">
-        <v>269</v>
+        <v>219</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H72" s="2" t="s">
-        <v>82</v>
-      </c>
+      <c r="H72" s="2"/>
       <c r="I72" s="2"/>
       <c r="J72" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="K72" s="23" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="73" ht="43.5" spans="1:11">
-      <c r="A73" s="21" t="s">
-        <v>271</v>
+        <v>68</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="73" ht="28" spans="1:11">
+      <c r="A73" s="17" t="s">
+        <v>268</v>
       </c>
       <c r="B73" s="14">
         <v>1</v>
       </c>
       <c r="C73" s="14" t="s">
-        <v>51</v>
+        <v>237</v>
       </c>
       <c r="D73" s="14" t="s">
         <v>19</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>273</v>
+        <v>219</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>143</v>
+        <v>35</v>
       </c>
       <c r="I73" s="2"/>
-      <c r="J73" s="3"/>
-      <c r="K73" s="24" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="74" ht="58" spans="1:11">
-      <c r="A74" s="19" t="s">
-        <v>275</v>
+      <c r="J73" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K73" s="3"/>
+    </row>
+    <row r="74" ht="42" spans="1:11">
+      <c r="A74" s="17" t="s">
+        <v>270</v>
       </c>
       <c r="B74" s="14">
         <v>1</v>
       </c>
       <c r="C74" s="14" t="s">
-        <v>38</v>
+        <v>237</v>
       </c>
       <c r="D74" s="14" t="s">
         <v>19</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H74" s="2"/>
       <c r="I74" s="2"/>
-      <c r="J74" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="K74" s="23" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="75" ht="42" spans="1:11">
-      <c r="A75" s="21" t="s">
-        <v>280</v>
+      <c r="J74" s="3"/>
+      <c r="K74" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="75" ht="28" spans="1:11">
+      <c r="A75" s="20" t="s">
+        <v>274</v>
       </c>
       <c r="B75" s="14">
         <v>1</v>
       </c>
       <c r="C75" s="14" t="s">
-        <v>69</v>
+        <v>237</v>
       </c>
       <c r="D75" s="14" t="s">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>282</v>
+        <v>242</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>143</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="H75" s="2"/>
       <c r="I75" s="2"/>
       <c r="J75" s="3"/>
-      <c r="K75" s="3" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="76" ht="28" spans="1:11">
-      <c r="A76" s="20" t="s">
-        <v>284</v>
+      <c r="K75" s="3"/>
+    </row>
+    <row r="76" ht="42" spans="1:11">
+      <c r="A76" s="17" t="s">
+        <v>276</v>
       </c>
       <c r="B76" s="14">
         <v>1</v>
       </c>
       <c r="C76" s="14" t="s">
-        <v>38</v>
+        <v>237</v>
       </c>
       <c r="D76" s="14" t="s">
         <v>13</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="H76" s="2"/>
-      <c r="I76" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>124</v>
-      </c>
+      <c r="I76" s="2"/>
+      <c r="J76" s="3"/>
       <c r="K76" s="3"/>
     </row>
-    <row r="77" ht="28" spans="1:11">
-      <c r="A77" s="19" t="s">
-        <v>287</v>
+    <row r="77" ht="42" spans="1:11">
+      <c r="A77" s="18" t="s">
+        <v>279</v>
       </c>
       <c r="B77" s="14">
         <v>1</v>
       </c>
       <c r="C77" s="14" t="s">
-        <v>51</v>
+        <v>237</v>
       </c>
       <c r="D77" s="14" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>34</v>
+        <v>281</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H77" s="2" t="s">
-        <v>82</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="H77" s="2"/>
       <c r="I77" s="2"/>
       <c r="J77" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="K77" s="3"/>
-    </row>
-    <row r="78" spans="1:11">
-      <c r="A78" s="17" t="s">
-        <v>290</v>
+        <v>36</v>
+      </c>
+      <c r="K77" s="3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="78" ht="56" spans="1:11">
+      <c r="A78" s="19" t="s">
+        <v>283</v>
       </c>
       <c r="B78" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C78" s="14" t="s">
-        <v>51</v>
+        <v>237</v>
       </c>
       <c r="D78" s="14" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>34</v>
+        <v>285</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H78" s="2"/>
+        <v>101</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="I78" s="2"/>
       <c r="J78" s="3" t="s">
-        <v>26</v>
+        <v>286</v>
       </c>
       <c r="K78" s="3"/>
     </row>
-    <row r="79" spans="1:11">
-      <c r="A79" s="17" t="s">
-        <v>292</v>
+    <row r="79" ht="56" spans="1:11">
+      <c r="A79" s="22" t="s">
+        <v>287</v>
       </c>
       <c r="B79" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79" s="14" t="s">
-        <v>51</v>
+        <v>237</v>
       </c>
       <c r="D79" s="14" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>34</v>
+        <v>289</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>22</v>
+        <v>200</v>
       </c>
       <c r="H79" s="2"/>
       <c r="I79" s="2"/>
       <c r="J79" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K79" s="3"/>
-    </row>
-    <row r="80" spans="1:11">
-      <c r="A80" s="17" t="s">
-        <v>294</v>
+        <v>151</v>
+      </c>
+      <c r="K79" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="80" ht="42" spans="1:11">
+      <c r="A80" s="20" t="s">
+        <v>290</v>
       </c>
       <c r="B80" s="14">
         <v>1</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>51</v>
+        <v>237</v>
       </c>
       <c r="D80" s="14" t="s">
-        <v>55</v>
+        <v>115</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>67</v>
+        <v>292</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>22</v>
@@ -4990,252 +4997,288 @@
       <c r="H80" s="2"/>
       <c r="I80" s="2"/>
       <c r="J80" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K80" s="3"/>
+        <v>68</v>
+      </c>
+      <c r="K80" s="3" t="s">
+        <v>293</v>
+      </c>
     </row>
     <row r="81" ht="42" spans="1:11">
-      <c r="A81" s="20" t="s">
-        <v>296</v>
+      <c r="A81" s="17" t="s">
+        <v>294</v>
       </c>
       <c r="B81" s="14">
         <v>1</v>
       </c>
       <c r="C81" s="14" t="s">
-        <v>51</v>
+        <v>237</v>
       </c>
       <c r="D81" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I81" s="2"/>
+      <c r="J81" s="3"/>
+      <c r="K81" s="3" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="82" ht="42" spans="1:11">
+      <c r="A82" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="B82" s="24">
+        <v>0</v>
+      </c>
+      <c r="C82" s="24" t="s">
+        <v>237</v>
+      </c>
+      <c r="D82" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="E81" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="G81" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="H81" s="2"/>
-      <c r="I81" s="2"/>
-      <c r="J81" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="K81" s="3"/>
-    </row>
-    <row r="82" ht="28" spans="1:11">
-      <c r="A82" s="17" t="s">
+      <c r="E82" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="B82" s="14">
-        <v>3</v>
-      </c>
-      <c r="C82" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D82" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E82" s="3" t="s">
+      <c r="F82" s="3" t="s">
         <v>300</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>301</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="I82" s="2"/>
-      <c r="J82" s="3"/>
-      <c r="K82" s="3"/>
+        <v>301</v>
+      </c>
+      <c r="I82" s="4"/>
+      <c r="J82" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="K82" s="5"/>
     </row>
     <row r="83" ht="42" spans="1:11">
-      <c r="A83" s="17" t="s">
-        <v>302</v>
-      </c>
-      <c r="B83" s="14">
-        <v>0</v>
-      </c>
-      <c r="C83" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D83" s="14" t="s">
+      <c r="A83" s="18" t="s">
+        <v>303</v>
+      </c>
+      <c r="B83" s="24">
+        <v>2</v>
+      </c>
+      <c r="C83" s="24" t="s">
+        <v>237</v>
+      </c>
+      <c r="D83" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>303</v>
+      <c r="E83" s="5" t="s">
+        <v>304</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H83" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I83" s="2"/>
-      <c r="J83" s="3"/>
-      <c r="K83" s="3"/>
-    </row>
-    <row r="84" ht="42" spans="1:11">
+      <c r="H83" s="2"/>
+      <c r="I83" s="4"/>
+      <c r="J83" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="K83" s="5"/>
+    </row>
+    <row r="84" ht="56" spans="1:11">
       <c r="A84" s="17" t="s">
-        <v>305</v>
-      </c>
-      <c r="B84" s="25">
+        <v>307</v>
+      </c>
+      <c r="B84" s="24">
         <v>0</v>
       </c>
-      <c r="C84" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="D84" s="25" t="s">
-        <v>13</v>
+      <c r="C84" s="24" t="s">
+        <v>237</v>
+      </c>
+      <c r="D84" s="24" t="s">
+        <v>115</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="F84" s="5" t="s">
-        <v>307</v>
+        <v>308</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>309</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H84" s="4" t="s">
-        <v>308</v>
+        <v>22</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>310</v>
       </c>
       <c r="I84" s="4"/>
       <c r="J84" s="5" t="s">
-        <v>309</v>
+        <v>26</v>
       </c>
       <c r="K84" s="5"/>
     </row>
     <row r="85" ht="42" spans="1:11">
-      <c r="A85" s="17" t="s">
-        <v>310</v>
-      </c>
-      <c r="B85" s="25">
-        <v>2</v>
-      </c>
-      <c r="C85" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="D85" s="25" t="s">
-        <v>13</v>
+      <c r="A85" s="20" t="s">
+        <v>311</v>
+      </c>
+      <c r="B85" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="C85" s="24" t="s">
+        <v>237</v>
+      </c>
+      <c r="D85" s="24" t="s">
+        <v>115</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="F85" s="5" t="s">
         <v>312</v>
       </c>
+      <c r="F85" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="G85" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H85" s="4"/>
+        <v>22</v>
+      </c>
+      <c r="H85" s="2"/>
       <c r="I85" s="4"/>
       <c r="J85" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="K85" s="5"/>
+    </row>
+    <row r="86" spans="1:11">
+      <c r="A86" s="20" t="s">
         <v>313</v>
       </c>
-      <c r="K85" s="5"/>
-    </row>
-    <row r="86" ht="56" spans="1:11">
-      <c r="A86" s="21" t="s">
+      <c r="B86" s="24">
+        <v>1</v>
+      </c>
+      <c r="C86" s="24" t="s">
+        <v>237</v>
+      </c>
+      <c r="D86" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="E86" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="B86" s="25">
-        <v>0</v>
-      </c>
-      <c r="C86" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="D86" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="E86" s="5" t="s">
+      <c r="F86" s="3" t="s">
         <v>315</v>
-      </c>
-      <c r="F86" s="5" t="s">
-        <v>316</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H86" s="4" t="s">
-        <v>317</v>
+      <c r="H86" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="I86" s="4"/>
       <c r="J86" s="5" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="K86" s="5"/>
     </row>
     <row r="87" ht="42" spans="1:11">
       <c r="A87" s="20" t="s">
+        <v>316</v>
+      </c>
+      <c r="B87" s="24">
+        <v>1</v>
+      </c>
+      <c r="C87" s="24" t="s">
+        <v>237</v>
+      </c>
+      <c r="D87" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E87" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="F87" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="B87" s="25" t="s">
-        <v>217</v>
-      </c>
-      <c r="C87" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="D87" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="E87" s="5" t="s">
+      <c r="G87" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H87" s="2"/>
+      <c r="I87" s="4"/>
+      <c r="J87" s="5"/>
+      <c r="K87" s="5"/>
+    </row>
+    <row r="88" ht="28" spans="1:11">
+      <c r="A88" s="18" t="s">
         <v>319</v>
       </c>
-      <c r="F87" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="G87" s="2" t="s">
+      <c r="B88" s="14">
+        <v>1</v>
+      </c>
+      <c r="C88" s="25" t="s">
+        <v>320</v>
+      </c>
+      <c r="D88" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I88" s="2"/>
+      <c r="J88" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K88" s="3" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="89" ht="70" spans="1:11">
+      <c r="A89" s="17" t="s">
+        <v>323</v>
+      </c>
+      <c r="B89" s="14">
+        <v>0</v>
+      </c>
+      <c r="C89" s="25" t="s">
+        <v>320</v>
+      </c>
+      <c r="D89" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G89" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H87" s="4"/>
-      <c r="I87" s="4"/>
-      <c r="J87" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="K87" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11">
-      <c r="A88" s="20" t="s">
-        <v>321</v>
-      </c>
-      <c r="B88" s="25">
-        <v>1</v>
-      </c>
-      <c r="C88" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="D88" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="F88" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="G88" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H88" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="I88" s="4"/>
-      <c r="J88" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="K88" s="5"/>
+      <c r="H89" s="2"/>
+      <c r="I89" s="2"/>
+      <c r="J89" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="K89" s="3"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K88" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K89" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A2:K89">
+      <sortCondition ref="C1" sortBy="cellColor" dxfId="0"/>
+    </sortState>
     <extLst>
       <etc:autoFilterAnalysis etc:version="v1" etc:showPane="0">
         <etc:analysisCharts>
@@ -5250,57 +5293,57 @@
     </extLst>
   </autoFilter>
   <conditionalFormatting sqref="C18">
-    <cfRule type="containsText" dxfId="0" priority="10" operator="between" text="Rare">
+    <cfRule type="containsText" dxfId="1" priority="10" operator="between" text="Rare">
       <formula>NOT(ISERROR(SEARCH("Rare",C18)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="11" operator="between" text="罕见">
+    <cfRule type="containsText" dxfId="2" priority="11" operator="between" text="罕见">
       <formula>NOT(ISERROR(SEARCH("罕见",C18)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="12" operator="between" text="普通">
+    <cfRule type="containsText" dxfId="3" priority="12" operator="between" text="普通">
       <formula>NOT(ISERROR(SEARCH("普通",C18)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:C29">
-    <cfRule type="containsText" dxfId="0" priority="5" operator="between" text="Rare">
+    <cfRule type="containsText" dxfId="1" priority="5" operator="between" text="Rare">
       <formula>NOT(ISERROR(SEARCH("Rare",C28)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="7" operator="between" text="罕见">
+    <cfRule type="containsText" dxfId="2" priority="7" operator="between" text="罕见">
       <formula>NOT(ISERROR(SEARCH("罕见",C28)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="9" operator="between" text="普通">
+    <cfRule type="containsText" dxfId="3" priority="9" operator="between" text="普通">
       <formula>NOT(ISERROR(SEARCH("普通",C28)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C30:C31">
-    <cfRule type="containsText" dxfId="0" priority="4" operator="between" text="Rare">
+    <cfRule type="containsText" dxfId="1" priority="4" operator="between" text="Rare">
       <formula>NOT(ISERROR(SEARCH("Rare",C30)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="6" operator="between" text="罕见">
+    <cfRule type="containsText" dxfId="2" priority="6" operator="between" text="罕见">
       <formula>NOT(ISERROR(SEARCH("罕见",C30)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="8" operator="between" text="普通">
+    <cfRule type="containsText" dxfId="3" priority="8" operator="between" text="普通">
       <formula>NOT(ISERROR(SEARCH("普通",C30)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C50:C52">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="between" text="Rare">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="between" text="Rare">
       <formula>NOT(ISERROR(SEARCH("Rare",C50)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="2" operator="between" text="罕见">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="between" text="罕见">
       <formula>NOT(ISERROR(SEARCH("罕见",C50)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="3" operator="between" text="普通">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="between" text="普通">
       <formula>NOT(ISERROR(SEARCH("普通",C50)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C17 C19:C27 C32:C49 C53:C1048576">
-    <cfRule type="containsText" dxfId="0" priority="13" operator="between" text="Rare">
+    <cfRule type="containsText" dxfId="1" priority="13" operator="between" text="Rare">
       <formula>NOT(ISERROR(SEARCH("Rare",C1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="15" operator="between" text="罕见">
+    <cfRule type="containsText" dxfId="2" priority="15" operator="between" text="罕见">
       <formula>NOT(ISERROR(SEARCH("罕见",C1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="16" operator="between" text="普通">
+    <cfRule type="containsText" dxfId="3" priority="16" operator="between" text="普通">
       <formula>NOT(ISERROR(SEARCH("普通",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5308,7 +5351,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C88 C2:C84 C85:C87 C89:C1048576">
       <formula1>"初始Basic,普通Common,罕见UnCommon,稀有Rare,先古Ancient,临时生成Token"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G88 G2:G85 G86:G87">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G88 G89 G2:G85 G86:G87">
       <formula1>"自身,单个敌人,单个队友,所有敌人,所有队友,随机敌人"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D87 D88:D1048576">
@@ -5324,7 +5367,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="16.0909090909091" customWidth="1"/>
@@ -5337,16 +5380,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>10</v>
@@ -5357,590 +5400,608 @@
         <v>26</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F2" s="3"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>332</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>330</v>
       </c>
       <c r="F3" s="3"/>
     </row>
     <row r="4" ht="42" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="5" ht="56" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="6" ht="28" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="7" ht="42" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>54</v>
+        <v>114</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="8" ht="28" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>75</v>
+        <v>243</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>72</v>
+        <v>240</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F9" s="3"/>
     </row>
     <row r="10" ht="28" spans="1:6">
       <c r="A10" s="2" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F10" s="3"/>
     </row>
     <row r="11" ht="56" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="12" ht="56" spans="1:6">
       <c r="A12" s="2" t="s">
-        <v>124</v>
+        <v>68</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2" t="s">
-        <v>106</v>
+        <v>140</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F13" s="3"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2" t="s">
-        <v>116</v>
+        <v>251</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F14" s="3"/>
     </row>
     <row r="15" ht="28" spans="1:6">
       <c r="A15" s="2" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="16" ht="28" spans="1:6">
       <c r="A16" s="2" t="s">
-        <v>152</v>
+        <v>259</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F17" s="3"/>
     </row>
     <row r="18" ht="28" spans="1:6">
       <c r="A18" s="2" t="s">
-        <v>158</v>
+        <v>265</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F18" s="3"/>
     </row>
     <row r="19" ht="28" spans="1:6">
       <c r="A19" s="2" t="s">
-        <v>191</v>
+        <v>270</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F19" s="3"/>
     </row>
     <row r="20" ht="28" spans="1:6">
       <c r="A20" s="2" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D20" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>330</v>
-      </c>
       <c r="F20" s="3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F21" s="3"/>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2" t="s">
-        <v>195</v>
+        <v>274</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F22" s="3"/>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2" t="s">
-        <v>225</v>
+        <v>323</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D23" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>332</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>330</v>
       </c>
       <c r="F23" s="3"/>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2" t="s">
-        <v>252</v>
+        <v>287</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="25" ht="28" spans="1:6">
       <c r="A25" s="2" t="s">
-        <v>267</v>
+        <v>209</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F25" s="3"/>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F26" s="3"/>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D27" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="E27" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="E27" s="4" t="s">
-        <v>330</v>
-      </c>
       <c r="F27" s="3" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="28" ht="70" spans="1:6">
       <c r="A28" s="2" t="s">
-        <v>290</v>
+        <v>221</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="29" ht="42" spans="1:6">
       <c r="A29" s="2" t="s">
-        <v>287</v>
+        <v>217</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="4" t="s">
-        <v>292</v>
+        <v>223</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F30" s="5"/>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="4" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D31" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="E31" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="E31" s="4" t="s">
-        <v>330</v>
-      </c>
       <c r="F31" s="5" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="32" ht="42" spans="1:6">
       <c r="A32" s="4" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E32" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="F32" s="5" t="s">
-        <v>380</v>
-      </c>
+      <c r="D33" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="F33" s="5"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F31" etc:filterBottomFollowUsedRange="0">
@@ -5967,10 +6028,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>
@@ -5994,32 +6055,32 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -6053,7 +6114,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -6061,39 +6122,39 @@
         <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>206</v>
+        <v>178</v>
       </c>
       <c r="B3" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="4" ht="112" spans="1:2">
       <c r="A4" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>91</v>
+        <v>64</v>
       </c>
       <c r="B5" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>109</v>
+        <v>143</v>
       </c>
       <c r="B6" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
   </sheetData>
@@ -6114,31 +6175,31 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="2" ht="28" spans="1:2">
       <c r="A2" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="3" ht="28" spans="1:2">
       <c r="A3" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
   </sheetData>
